--- a/product-definitions/spreadsheet/particle-size-distribution-cloud.xlsx
+++ b/product-definitions/spreadsheet/particle-size-distribution-cloud.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="88">
   <si>
     <t>Name</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>min area, max area, min shape, max shape, min IAT, max IAT, edge rej, min N, max N, min area frac, max area frac, min aspect ratio, max aspect ratio, width min, width max, streak, CoM, grey Mode, zd threshold</t>
+  </si>
+  <si>
+    <t>exact match</t>
   </si>
   <si>
     <t>Length</t>
@@ -366,7 +369,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="33">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -387,10 +390,10 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left"/>
+      <alignment readingOrder="0" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -414,9 +417,6 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -430,9 +430,7 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -440,15 +438,11 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
@@ -773,17 +767,19 @@
       <c r="Z2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3"/>
+      <c r="E3" s="8" t="s">
+        <v>13</v>
+      </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -7683,7 +7679,6 @@
     <col customWidth="1" min="3" max="3" width="45.63"/>
     <col customWidth="1" min="4" max="13" width="8.75"/>
     <col customWidth="1" min="14" max="23" width="17.25"/>
-    <col customWidth="1" min="24" max="26" width="14.38"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.0" customHeight="1">
@@ -7691,10 +7686,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
@@ -7709,10 +7704,10 @@
     </row>
     <row r="2" ht="12.0" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="4">
         <v>1.0</v>
@@ -9237,24 +9232,24 @@
     <col customWidth="1" min="5" max="5" width="17.13"/>
     <col customWidth="1" min="6" max="6" width="17.63"/>
     <col customWidth="1" min="7" max="10" width="8.75"/>
-    <col customWidth="1" min="11" max="26" width="14.38"/>
+    <col customWidth="1" min="11" max="25" width="14.38"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.0" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="17" t="s">
         <v>21</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>22</v>
       </c>
       <c r="F1" s="16"/>
       <c r="G1" s="6"/>
@@ -9279,10 +9274,10 @@
     </row>
     <row r="2" ht="12.0" customHeight="1">
       <c r="A2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="10"/>
-      <c r="C2" s="18"/>
+      <c r="C2" s="17"/>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -9309,10 +9304,10 @@
     <row r="3" ht="12.0" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="18" t="s">
         <v>24</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -9340,10 +9335,10 @@
     <row r="4" ht="12.0" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -9371,10 +9366,10 @@
     <row r="5" ht="12.0" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>26</v>
+        <v>15</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>27</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -9402,11 +9397,11 @@
     <row r="6" ht="12.0" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="8"/>
+        <v>28</v>
+      </c>
+      <c r="C6" s="7"/>
       <c r="D6" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -9433,10 +9428,10 @@
     <row r="7" ht="12.0" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="8" t="s">
         <v>29</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -9464,10 +9459,10 @@
     <row r="8" ht="12.0" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="19" t="s">
         <v>31</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -9495,10 +9490,10 @@
     <row r="9" ht="12.0" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>32</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>31</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -9526,10 +9521,10 @@
     <row r="10" ht="12.0" customHeight="1">
       <c r="A10" s="14"/>
       <c r="B10" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -9564,7 +9559,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
-      <c r="J11" s="18"/>
+      <c r="J11" s="17"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
@@ -9583,17 +9578,17 @@
     </row>
     <row r="12" ht="12.0" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12" s="10"/>
-      <c r="C12" s="18"/>
+      <c r="C12" s="17"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
-      <c r="J12" s="18"/>
+      <c r="J12" s="17"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
@@ -9613,10 +9608,10 @@
     <row r="13" ht="12.0" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="18" t="s">
         <v>24</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -9624,7 +9619,7 @@
       <c r="G13" s="6"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
-      <c r="J13" s="18"/>
+      <c r="J13" s="17"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
@@ -9644,10 +9639,10 @@
     <row r="14" ht="12.0" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -9655,7 +9650,7 @@
       <c r="G14" s="6"/>
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
-      <c r="J14" s="18"/>
+      <c r="J14" s="17"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
@@ -9675,10 +9670,10 @@
     <row r="15" ht="12.0" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>26</v>
+        <v>15</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>27</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -9686,7 +9681,7 @@
       <c r="G15" s="6"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
-      <c r="J15" s="18"/>
+      <c r="J15" s="17"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
@@ -9706,18 +9701,18 @@
     <row r="16" ht="12.0" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="20" t="s">
-        <v>35</v>
+        <v>28</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
-      <c r="J16" s="18"/>
+      <c r="J16" s="17"/>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
@@ -9737,10 +9732,10 @@
     <row r="17" ht="12.0" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>36</v>
+        <v>29</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -9748,7 +9743,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="18"/>
+      <c r="J17" s="17"/>
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
@@ -9768,10 +9763,10 @@
     <row r="18" ht="12.0" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="19" t="s">
         <v>31</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -9779,7 +9774,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="18"/>
+      <c r="J18" s="17"/>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
@@ -9799,10 +9794,10 @@
     <row r="19" ht="12.0" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>32</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>31</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -9810,7 +9805,7 @@
       <c r="G19" s="6"/>
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="18"/>
+      <c r="J19" s="17"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
@@ -9830,10 +9825,10 @@
     <row r="20" ht="12.0" customHeight="1">
       <c r="A20" s="14"/>
       <c r="B20" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
@@ -9841,7 +9836,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="18"/>
+      <c r="J20" s="17"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
@@ -9868,7 +9863,7 @@
       <c r="G21" s="6"/>
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="18"/>
+      <c r="J21" s="17"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
@@ -9887,17 +9882,17 @@
     </row>
     <row r="22" ht="12.0" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="10"/>
-      <c r="C22" s="18"/>
+      <c r="C22" s="17"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="18"/>
+      <c r="J22" s="17"/>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
@@ -9917,10 +9912,10 @@
     <row r="23" ht="12.0" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="18" t="s">
         <v>24</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -9928,7 +9923,7 @@
       <c r="G23" s="6"/>
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="18"/>
+      <c r="J23" s="17"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
@@ -9948,10 +9943,10 @@
     <row r="24" ht="12.0" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
@@ -9959,7 +9954,7 @@
       <c r="G24" s="6"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
-      <c r="J24" s="18"/>
+      <c r="J24" s="17"/>
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
@@ -9979,10 +9974,10 @@
     <row r="25" ht="12.0" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>26</v>
+        <v>15</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>27</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -9990,7 +9985,7 @@
       <c r="G25" s="6"/>
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
-      <c r="J25" s="18"/>
+      <c r="J25" s="17"/>
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
@@ -10010,18 +10005,18 @@
     <row r="26" ht="12.0" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="20" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="19" t="s">
+        <v>38</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="10"/>
       <c r="I26" s="10"/>
-      <c r="J26" s="18"/>
+      <c r="J26" s="17"/>
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
@@ -10041,10 +10036,10 @@
     <row r="27" ht="12.0" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -10052,7 +10047,7 @@
       <c r="G27" s="6"/>
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
-      <c r="J27" s="18"/>
+      <c r="J27" s="17"/>
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
@@ -10072,10 +10067,10 @@
     <row r="28" ht="12.0" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="19" t="s">
         <v>31</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
@@ -10083,7 +10078,7 @@
       <c r="G28" s="6"/>
       <c r="H28" s="10"/>
       <c r="I28" s="10"/>
-      <c r="J28" s="18"/>
+      <c r="J28" s="17"/>
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
@@ -10103,10 +10098,10 @@
     <row r="29" ht="12.0" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="18" t="s">
         <v>32</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>31</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -10114,7 +10109,7 @@
       <c r="G29" s="6"/>
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
-      <c r="J29" s="18"/>
+      <c r="J29" s="17"/>
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
@@ -10134,10 +10129,10 @@
     <row r="30" ht="12.0" customHeight="1">
       <c r="A30" s="14"/>
       <c r="B30" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
@@ -10145,7 +10140,7 @@
       <c r="G30" s="6"/>
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
-      <c r="J30" s="18"/>
+      <c r="J30" s="17"/>
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
@@ -10172,7 +10167,7 @@
       <c r="G31" s="6"/>
       <c r="H31" s="10"/>
       <c r="I31" s="10"/>
-      <c r="J31" s="18"/>
+      <c r="J31" s="17"/>
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
@@ -10191,7 +10186,7 @@
     </row>
     <row r="32" ht="12.0" customHeight="1">
       <c r="A32" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="15"/>
@@ -10201,7 +10196,7 @@
       <c r="G32" s="6"/>
       <c r="H32" s="10"/>
       <c r="I32" s="10"/>
-      <c r="J32" s="18"/>
+      <c r="J32" s="17"/>
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
@@ -10221,10 +10216,10 @@
     <row r="33" ht="12.0" customHeight="1">
       <c r="A33" s="14"/>
       <c r="B33" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="18" t="s">
         <v>24</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -10232,7 +10227,7 @@
       <c r="G33" s="6"/>
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
-      <c r="J33" s="18"/>
+      <c r="J33" s="17"/>
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
@@ -10252,10 +10247,10 @@
     <row r="34" ht="12.0" customHeight="1">
       <c r="A34" s="14"/>
       <c r="B34" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -10263,7 +10258,7 @@
       <c r="G34" s="6"/>
       <c r="H34" s="10"/>
       <c r="I34" s="10"/>
-      <c r="J34" s="18"/>
+      <c r="J34" s="17"/>
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
@@ -10283,10 +10278,10 @@
     <row r="35" ht="12.0" customHeight="1">
       <c r="A35" s="14"/>
       <c r="B35" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>41</v>
+        <v>15</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>42</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -10294,7 +10289,7 @@
       <c r="G35" s="6"/>
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
-      <c r="J35" s="18"/>
+      <c r="J35" s="17"/>
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
@@ -10314,18 +10309,18 @@
     <row r="36" ht="12.0" customHeight="1">
       <c r="A36" s="14"/>
       <c r="B36" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C36" s="15"/>
       <c r="D36" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
-      <c r="J36" s="18"/>
+      <c r="J36" s="17"/>
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
@@ -10345,10 +10340,10 @@
     <row r="37" ht="12.0" customHeight="1">
       <c r="A37" s="14"/>
       <c r="B37" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -10356,7 +10351,7 @@
       <c r="G37" s="6"/>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
-      <c r="J37" s="18"/>
+      <c r="J37" s="17"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
@@ -10376,9 +10371,9 @@
     <row r="38" ht="12.0" customHeight="1">
       <c r="A38" s="14"/>
       <c r="B38" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="21">
+        <v>44</v>
+      </c>
+      <c r="C38" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D38" s="6"/>
@@ -10387,7 +10382,7 @@
       <c r="G38" s="6"/>
       <c r="H38" s="10"/>
       <c r="I38" s="10"/>
-      <c r="J38" s="18"/>
+      <c r="J38" s="17"/>
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
@@ -10407,10 +10402,10 @@
     <row r="39" ht="12.0" customHeight="1">
       <c r="A39" s="14"/>
       <c r="B39" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="19" t="s">
         <v>31</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
@@ -10418,7 +10413,7 @@
       <c r="G39" s="6"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
-      <c r="J39" s="18"/>
+      <c r="J39" s="17"/>
       <c r="K39" s="6"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
@@ -10438,10 +10433,10 @@
     <row r="40" ht="12.0" customHeight="1">
       <c r="A40" s="14"/>
       <c r="B40" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="18" t="s">
         <v>32</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>31</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -10449,7 +10444,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="10"/>
       <c r="I40" s="10"/>
-      <c r="J40" s="18"/>
+      <c r="J40" s="17"/>
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
@@ -10468,17 +10463,17 @@
     </row>
     <row r="41" ht="12.0" customHeight="1">
       <c r="A41" s="14"/>
-      <c r="B41" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" s="18"/>
+      <c r="B41" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="17"/>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="10"/>
       <c r="I41" s="10"/>
-      <c r="J41" s="18"/>
+      <c r="J41" s="17"/>
       <c r="K41" s="6"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
@@ -10498,10 +10493,10 @@
     <row r="42" ht="12.0" customHeight="1">
       <c r="A42" s="14"/>
       <c r="B42" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
@@ -10509,7 +10504,7 @@
       <c r="G42" s="6"/>
       <c r="H42" s="10"/>
       <c r="I42" s="10"/>
-      <c r="J42" s="18"/>
+      <c r="J42" s="17"/>
       <c r="K42" s="6"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
@@ -10536,7 +10531,7 @@
       <c r="G43" s="6"/>
       <c r="H43" s="10"/>
       <c r="I43" s="10"/>
-      <c r="J43" s="18"/>
+      <c r="J43" s="17"/>
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
@@ -10555,7 +10550,7 @@
     </row>
     <row r="44" ht="12.0" customHeight="1">
       <c r="A44" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B44" s="10"/>
       <c r="C44" s="11"/>
@@ -10585,10 +10580,10 @@
     <row r="45" ht="12.0" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
@@ -10616,10 +10611,10 @@
     <row r="46" ht="12.0" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
@@ -10647,10 +10642,10 @@
     <row r="47" ht="12.0" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
@@ -10678,11 +10673,11 @@
     <row r="48" ht="12.0" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
@@ -10709,10 +10704,10 @@
     <row r="49" ht="12.0" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
@@ -10720,7 +10715,7 @@
       <c r="G49" s="6"/>
       <c r="H49" s="10"/>
       <c r="I49" s="6"/>
-      <c r="J49" s="22"/>
+      <c r="J49" s="21"/>
       <c r="K49" s="6"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
@@ -10740,9 +10735,9 @@
     <row r="50" ht="12.0" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C50" s="21">
+        <v>44</v>
+      </c>
+      <c r="C50" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D50" s="6"/>
@@ -10771,10 +10766,10 @@
     <row r="51" ht="12.0" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C51" s="19" t="s">
         <v>31</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
@@ -10802,10 +10797,10 @@
     <row r="52" ht="12.0" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C52" s="18" t="s">
         <v>32</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>31</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
@@ -10832,13 +10827,13 @@
     </row>
     <row r="53" ht="12.0" customHeight="1">
       <c r="A53" s="10"/>
-      <c r="B53" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C53" s="18"/>
+      <c r="B53" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="17"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
@@ -10864,10 +10859,10 @@
     <row r="54" ht="12.0" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
@@ -10921,412 +10916,412 @@
       <c r="Z55" s="10"/>
     </row>
     <row r="56" ht="12.0" customHeight="1">
-      <c r="A56" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="B56" s="24"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="26"/>
-      <c r="J56" s="25"/>
-      <c r="K56" s="26"/>
-      <c r="L56" s="26"/>
-      <c r="M56" s="26"/>
-      <c r="N56" s="26"/>
-      <c r="O56" s="26"/>
-      <c r="P56" s="26"/>
-      <c r="Q56" s="26"/>
-      <c r="R56" s="26"/>
-      <c r="S56" s="26"/>
-      <c r="T56" s="26"/>
-      <c r="U56" s="26"/>
-      <c r="V56" s="26"/>
-      <c r="W56" s="26"/>
-      <c r="X56" s="26"/>
-      <c r="Y56" s="26"/>
-      <c r="Z56" s="26"/>
+      <c r="A56" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B56" s="23"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="25"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="24"/>
+      <c r="K56" s="25"/>
+      <c r="L56" s="25"/>
+      <c r="M56" s="25"/>
+      <c r="N56" s="25"/>
+      <c r="O56" s="25"/>
+      <c r="P56" s="25"/>
+      <c r="Q56" s="25"/>
+      <c r="R56" s="25"/>
+      <c r="S56" s="25"/>
+      <c r="T56" s="25"/>
+      <c r="U56" s="25"/>
+      <c r="V56" s="25"/>
+      <c r="W56" s="25"/>
+      <c r="X56" s="25"/>
+      <c r="Y56" s="25"/>
+      <c r="Z56" s="25"/>
     </row>
     <row r="57" ht="12.0" customHeight="1">
-      <c r="A57" s="24"/>
-      <c r="B57" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C57" s="28" t="s">
+      <c r="A57" s="23"/>
+      <c r="B57" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-      <c r="J57" s="28"/>
-      <c r="K57" s="27"/>
-      <c r="L57" s="27"/>
-      <c r="M57" s="27"/>
-      <c r="N57" s="27"/>
-      <c r="O57" s="27"/>
-      <c r="P57" s="27"/>
-      <c r="Q57" s="27"/>
-      <c r="R57" s="27"/>
-      <c r="S57" s="27"/>
-      <c r="T57" s="27"/>
-      <c r="U57" s="27"/>
-      <c r="V57" s="27"/>
-      <c r="W57" s="27"/>
-      <c r="X57" s="27"/>
-      <c r="Y57" s="27"/>
-      <c r="Z57" s="27"/>
+      <c r="C57" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="22"/>
+      <c r="J57" s="26"/>
+      <c r="K57" s="22"/>
+      <c r="L57" s="22"/>
+      <c r="M57" s="22"/>
+      <c r="N57" s="22"/>
+      <c r="O57" s="22"/>
+      <c r="P57" s="22"/>
+      <c r="Q57" s="22"/>
+      <c r="R57" s="22"/>
+      <c r="S57" s="22"/>
+      <c r="T57" s="22"/>
+      <c r="U57" s="22"/>
+      <c r="V57" s="22"/>
+      <c r="W57" s="22"/>
+      <c r="X57" s="22"/>
+      <c r="Y57" s="22"/>
+      <c r="Z57" s="22"/>
     </row>
     <row r="58" ht="12.0" customHeight="1">
-      <c r="A58" s="24"/>
-      <c r="B58" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C58" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="28"/>
-      <c r="K58" s="27"/>
-      <c r="L58" s="27"/>
-      <c r="M58" s="27"/>
-      <c r="N58" s="27"/>
-      <c r="O58" s="27"/>
-      <c r="P58" s="27"/>
-      <c r="Q58" s="27"/>
-      <c r="R58" s="27"/>
-      <c r="S58" s="27"/>
-      <c r="T58" s="27"/>
-      <c r="U58" s="27"/>
-      <c r="V58" s="27"/>
-      <c r="W58" s="27"/>
-      <c r="X58" s="27"/>
-      <c r="Y58" s="27"/>
-      <c r="Z58" s="27"/>
+      <c r="A58" s="23"/>
+      <c r="B58" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="26"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="22"/>
+      <c r="M58" s="22"/>
+      <c r="N58" s="22"/>
+      <c r="O58" s="22"/>
+      <c r="P58" s="22"/>
+      <c r="Q58" s="22"/>
+      <c r="R58" s="22"/>
+      <c r="S58" s="22"/>
+      <c r="T58" s="22"/>
+      <c r="U58" s="22"/>
+      <c r="V58" s="22"/>
+      <c r="W58" s="22"/>
+      <c r="X58" s="22"/>
+      <c r="Y58" s="22"/>
+      <c r="Z58" s="22"/>
     </row>
     <row r="59" ht="12.0" customHeight="1">
-      <c r="A59" s="24"/>
-      <c r="B59" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C59" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27"/>
-      <c r="J59" s="28"/>
-      <c r="K59" s="27"/>
-      <c r="L59" s="27"/>
-      <c r="M59" s="27"/>
-      <c r="N59" s="27"/>
-      <c r="O59" s="27"/>
-      <c r="P59" s="27"/>
-      <c r="Q59" s="27"/>
-      <c r="R59" s="27"/>
-      <c r="S59" s="27"/>
-      <c r="T59" s="27"/>
-      <c r="U59" s="27"/>
-      <c r="V59" s="27"/>
-      <c r="W59" s="27"/>
-      <c r="X59" s="27"/>
-      <c r="Y59" s="27"/>
-      <c r="Z59" s="27"/>
+      <c r="A59" s="23"/>
+      <c r="B59" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="22"/>
+      <c r="J59" s="26"/>
+      <c r="K59" s="22"/>
+      <c r="L59" s="22"/>
+      <c r="M59" s="22"/>
+      <c r="N59" s="22"/>
+      <c r="O59" s="22"/>
+      <c r="P59" s="22"/>
+      <c r="Q59" s="22"/>
+      <c r="R59" s="22"/>
+      <c r="S59" s="22"/>
+      <c r="T59" s="22"/>
+      <c r="U59" s="22"/>
+      <c r="V59" s="22"/>
+      <c r="W59" s="22"/>
+      <c r="X59" s="22"/>
+      <c r="Y59" s="22"/>
+      <c r="Z59" s="22"/>
     </row>
     <row r="60" ht="12.0" customHeight="1">
-      <c r="A60" s="24"/>
-      <c r="B60" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C60" s="25"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="27"/>
-      <c r="I60" s="27"/>
-      <c r="J60" s="28"/>
-      <c r="K60" s="27"/>
-      <c r="L60" s="27"/>
-      <c r="M60" s="27"/>
-      <c r="N60" s="27"/>
-      <c r="O60" s="27"/>
-      <c r="P60" s="27"/>
-      <c r="Q60" s="27"/>
-      <c r="R60" s="27"/>
-      <c r="S60" s="27"/>
-      <c r="T60" s="27"/>
-      <c r="U60" s="27"/>
-      <c r="V60" s="27"/>
-      <c r="W60" s="27"/>
-      <c r="X60" s="27"/>
-      <c r="Y60" s="27"/>
-      <c r="Z60" s="27"/>
+      <c r="A60" s="23"/>
+      <c r="B60" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" s="24"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="22"/>
+      <c r="H60" s="22"/>
+      <c r="I60" s="22"/>
+      <c r="J60" s="26"/>
+      <c r="K60" s="22"/>
+      <c r="L60" s="22"/>
+      <c r="M60" s="22"/>
+      <c r="N60" s="22"/>
+      <c r="O60" s="22"/>
+      <c r="P60" s="22"/>
+      <c r="Q60" s="22"/>
+      <c r="R60" s="22"/>
+      <c r="S60" s="22"/>
+      <c r="T60" s="22"/>
+      <c r="U60" s="22"/>
+      <c r="V60" s="22"/>
+      <c r="W60" s="22"/>
+      <c r="X60" s="22"/>
+      <c r="Y60" s="22"/>
+      <c r="Z60" s="22"/>
     </row>
     <row r="61" ht="12.0" customHeight="1">
-      <c r="A61" s="24"/>
-      <c r="B61" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C61" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="28"/>
-      <c r="K61" s="27"/>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
-      <c r="N61" s="27"/>
-      <c r="O61" s="27"/>
-      <c r="P61" s="27"/>
-      <c r="Q61" s="27"/>
-      <c r="R61" s="27"/>
-      <c r="S61" s="27"/>
-      <c r="T61" s="27"/>
-      <c r="U61" s="27"/>
-      <c r="V61" s="27"/>
-      <c r="W61" s="27"/>
-      <c r="X61" s="27"/>
-      <c r="Y61" s="27"/>
-      <c r="Z61" s="27"/>
+      <c r="A61" s="23"/>
+      <c r="B61" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C61" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="22"/>
+      <c r="I61" s="22"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="22"/>
+      <c r="L61" s="22"/>
+      <c r="M61" s="22"/>
+      <c r="N61" s="22"/>
+      <c r="O61" s="22"/>
+      <c r="P61" s="22"/>
+      <c r="Q61" s="22"/>
+      <c r="R61" s="22"/>
+      <c r="S61" s="22"/>
+      <c r="T61" s="22"/>
+      <c r="U61" s="22"/>
+      <c r="V61" s="22"/>
+      <c r="W61" s="22"/>
+      <c r="X61" s="22"/>
+      <c r="Y61" s="22"/>
+      <c r="Z61" s="22"/>
     </row>
     <row r="62" ht="12.0" customHeight="1">
-      <c r="A62" s="24"/>
-      <c r="B62" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C62" s="31">
+      <c r="A62" s="23"/>
+      <c r="B62" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C62" s="28">
         <v>-1.0E20</v>
       </c>
-      <c r="D62" s="27"/>
-      <c r="E62" s="27"/>
-      <c r="F62" s="27"/>
-      <c r="G62" s="27"/>
-      <c r="H62" s="27"/>
-      <c r="I62" s="27"/>
-      <c r="J62" s="28"/>
-      <c r="K62" s="27"/>
-      <c r="L62" s="27"/>
-      <c r="M62" s="27"/>
-      <c r="N62" s="27"/>
-      <c r="O62" s="27"/>
-      <c r="P62" s="27"/>
-      <c r="Q62" s="27"/>
-      <c r="R62" s="27"/>
-      <c r="S62" s="27"/>
-      <c r="T62" s="27"/>
-      <c r="U62" s="27"/>
-      <c r="V62" s="27"/>
-      <c r="W62" s="27"/>
-      <c r="X62" s="27"/>
-      <c r="Y62" s="27"/>
-      <c r="Z62" s="27"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="26"/>
+      <c r="K62" s="22"/>
+      <c r="L62" s="22"/>
+      <c r="M62" s="22"/>
+      <c r="N62" s="22"/>
+      <c r="O62" s="22"/>
+      <c r="P62" s="22"/>
+      <c r="Q62" s="22"/>
+      <c r="R62" s="22"/>
+      <c r="S62" s="22"/>
+      <c r="T62" s="22"/>
+      <c r="U62" s="22"/>
+      <c r="V62" s="22"/>
+      <c r="W62" s="22"/>
+      <c r="X62" s="22"/>
+      <c r="Y62" s="22"/>
+      <c r="Z62" s="22"/>
     </row>
     <row r="63" ht="12.0" customHeight="1">
-      <c r="A63" s="24"/>
-      <c r="B63" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C63" s="32" t="s">
+      <c r="A63" s="23"/>
+      <c r="B63" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="27"/>
-      <c r="J63" s="28"/>
-      <c r="K63" s="27"/>
-      <c r="L63" s="27"/>
-      <c r="M63" s="27"/>
-      <c r="N63" s="27"/>
-      <c r="O63" s="27"/>
-      <c r="P63" s="27"/>
-      <c r="Q63" s="27"/>
-      <c r="R63" s="27"/>
-      <c r="S63" s="27"/>
-      <c r="T63" s="27"/>
-      <c r="U63" s="27"/>
-      <c r="V63" s="27"/>
-      <c r="W63" s="27"/>
-      <c r="X63" s="27"/>
-      <c r="Y63" s="27"/>
-      <c r="Z63" s="27"/>
+      <c r="C63" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="26"/>
+      <c r="K63" s="22"/>
+      <c r="L63" s="22"/>
+      <c r="M63" s="22"/>
+      <c r="N63" s="22"/>
+      <c r="O63" s="22"/>
+      <c r="P63" s="22"/>
+      <c r="Q63" s="22"/>
+      <c r="R63" s="22"/>
+      <c r="S63" s="22"/>
+      <c r="T63" s="22"/>
+      <c r="U63" s="22"/>
+      <c r="V63" s="22"/>
+      <c r="W63" s="22"/>
+      <c r="X63" s="22"/>
+      <c r="Y63" s="22"/>
+      <c r="Z63" s="22"/>
     </row>
     <row r="64" ht="12.0" customHeight="1">
-      <c r="A64" s="24"/>
-      <c r="B64" s="27" t="s">
+      <c r="A64" s="23"/>
+      <c r="B64" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C64" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="C64" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="27"/>
-      <c r="J64" s="28"/>
-      <c r="K64" s="27"/>
-      <c r="L64" s="27"/>
-      <c r="M64" s="27"/>
-      <c r="N64" s="27"/>
-      <c r="O64" s="27"/>
-      <c r="P64" s="27"/>
-      <c r="Q64" s="27"/>
-      <c r="R64" s="27"/>
-      <c r="S64" s="27"/>
-      <c r="T64" s="27"/>
-      <c r="U64" s="27"/>
-      <c r="V64" s="27"/>
-      <c r="W64" s="27"/>
-      <c r="X64" s="27"/>
-      <c r="Y64" s="27"/>
-      <c r="Z64" s="27"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="22"/>
+      <c r="I64" s="22"/>
+      <c r="J64" s="26"/>
+      <c r="K64" s="22"/>
+      <c r="L64" s="22"/>
+      <c r="M64" s="22"/>
+      <c r="N64" s="22"/>
+      <c r="O64" s="22"/>
+      <c r="P64" s="22"/>
+      <c r="Q64" s="22"/>
+      <c r="R64" s="22"/>
+      <c r="S64" s="22"/>
+      <c r="T64" s="22"/>
+      <c r="U64" s="22"/>
+      <c r="V64" s="22"/>
+      <c r="W64" s="22"/>
+      <c r="X64" s="22"/>
+      <c r="Y64" s="22"/>
+      <c r="Z64" s="22"/>
     </row>
     <row r="65" ht="12.0" customHeight="1">
-      <c r="A65" s="24"/>
-      <c r="B65" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C65" s="28"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="27"/>
-      <c r="H65" s="27"/>
-      <c r="I65" s="27"/>
-      <c r="J65" s="28"/>
-      <c r="K65" s="27"/>
-      <c r="L65" s="27"/>
-      <c r="M65" s="27"/>
-      <c r="N65" s="27"/>
-      <c r="O65" s="27"/>
-      <c r="P65" s="27"/>
-      <c r="Q65" s="27"/>
-      <c r="R65" s="27"/>
-      <c r="S65" s="27"/>
-      <c r="T65" s="27"/>
-      <c r="U65" s="27"/>
-      <c r="V65" s="27"/>
-      <c r="W65" s="27"/>
-      <c r="X65" s="27"/>
-      <c r="Y65" s="27"/>
-      <c r="Z65" s="27"/>
+      <c r="A65" s="23"/>
+      <c r="B65" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C65" s="26"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="22"/>
+      <c r="H65" s="22"/>
+      <c r="I65" s="22"/>
+      <c r="J65" s="26"/>
+      <c r="K65" s="22"/>
+      <c r="L65" s="22"/>
+      <c r="M65" s="22"/>
+      <c r="N65" s="22"/>
+      <c r="O65" s="22"/>
+      <c r="P65" s="22"/>
+      <c r="Q65" s="22"/>
+      <c r="R65" s="22"/>
+      <c r="S65" s="22"/>
+      <c r="T65" s="22"/>
+      <c r="U65" s="22"/>
+      <c r="V65" s="22"/>
+      <c r="W65" s="22"/>
+      <c r="X65" s="22"/>
+      <c r="Y65" s="22"/>
+      <c r="Z65" s="22"/>
     </row>
     <row r="66" ht="12.0" customHeight="1">
-      <c r="A66" s="24"/>
-      <c r="B66" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C66" s="29" t="s">
+      <c r="A66" s="23"/>
+      <c r="B66" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D66" s="27"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="27"/>
-      <c r="J66" s="28"/>
-      <c r="K66" s="27"/>
-      <c r="L66" s="27"/>
-      <c r="M66" s="27"/>
-      <c r="N66" s="27"/>
-      <c r="O66" s="27"/>
-      <c r="P66" s="27"/>
-      <c r="Q66" s="27"/>
-      <c r="R66" s="27"/>
-      <c r="S66" s="27"/>
-      <c r="T66" s="27"/>
-      <c r="U66" s="27"/>
-      <c r="V66" s="27"/>
-      <c r="W66" s="27"/>
-      <c r="X66" s="27"/>
-      <c r="Y66" s="27"/>
-      <c r="Z66" s="27"/>
+      <c r="C66" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="22"/>
+      <c r="I66" s="22"/>
+      <c r="J66" s="26"/>
+      <c r="K66" s="22"/>
+      <c r="L66" s="22"/>
+      <c r="M66" s="22"/>
+      <c r="N66" s="22"/>
+      <c r="O66" s="22"/>
+      <c r="P66" s="22"/>
+      <c r="Q66" s="22"/>
+      <c r="R66" s="22"/>
+      <c r="S66" s="22"/>
+      <c r="T66" s="22"/>
+      <c r="U66" s="22"/>
+      <c r="V66" s="22"/>
+      <c r="W66" s="22"/>
+      <c r="X66" s="22"/>
+      <c r="Y66" s="22"/>
+      <c r="Z66" s="22"/>
     </row>
     <row r="67" ht="12.0" customHeight="1">
-      <c r="A67" s="24"/>
-      <c r="B67" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C67" s="29"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="28"/>
-      <c r="K67" s="27"/>
-      <c r="L67" s="27"/>
-      <c r="M67" s="27"/>
-      <c r="N67" s="27"/>
-      <c r="O67" s="27"/>
-      <c r="P67" s="27"/>
-      <c r="Q67" s="27"/>
-      <c r="R67" s="27"/>
-      <c r="S67" s="27"/>
-      <c r="T67" s="27"/>
-      <c r="U67" s="27"/>
-      <c r="V67" s="27"/>
-      <c r="W67" s="27"/>
-      <c r="X67" s="27"/>
-      <c r="Y67" s="27"/>
-      <c r="Z67" s="27"/>
+      <c r="A67" s="23"/>
+      <c r="B67" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C67" s="27"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="26"/>
+      <c r="K67" s="22"/>
+      <c r="L67" s="22"/>
+      <c r="M67" s="22"/>
+      <c r="N67" s="22"/>
+      <c r="O67" s="22"/>
+      <c r="P67" s="22"/>
+      <c r="Q67" s="22"/>
+      <c r="R67" s="22"/>
+      <c r="S67" s="22"/>
+      <c r="T67" s="22"/>
+      <c r="U67" s="22"/>
+      <c r="V67" s="22"/>
+      <c r="W67" s="22"/>
+      <c r="X67" s="22"/>
+      <c r="Y67" s="22"/>
+      <c r="Z67" s="22"/>
     </row>
     <row r="68" ht="12.0" customHeight="1">
-      <c r="A68" s="24"/>
-      <c r="B68" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C68" s="29" t="s">
+      <c r="A68" s="23"/>
+      <c r="B68" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="D68" s="27"/>
-      <c r="E68" s="27"/>
-      <c r="F68" s="27"/>
-      <c r="G68" s="27"/>
-      <c r="H68" s="27"/>
-      <c r="I68" s="27"/>
-      <c r="J68" s="28"/>
-      <c r="K68" s="27"/>
-      <c r="L68" s="27"/>
-      <c r="M68" s="27"/>
-      <c r="N68" s="27"/>
-      <c r="O68" s="27"/>
-      <c r="P68" s="27"/>
-      <c r="Q68" s="27"/>
-      <c r="R68" s="27"/>
-      <c r="S68" s="27"/>
-      <c r="T68" s="27"/>
-      <c r="U68" s="27"/>
-      <c r="V68" s="27"/>
-      <c r="W68" s="27"/>
-      <c r="X68" s="27"/>
-      <c r="Y68" s="27"/>
-      <c r="Z68" s="27"/>
+      <c r="C68" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="26"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="22"/>
+      <c r="M68" s="22"/>
+      <c r="N68" s="22"/>
+      <c r="O68" s="22"/>
+      <c r="P68" s="22"/>
+      <c r="Q68" s="22"/>
+      <c r="R68" s="22"/>
+      <c r="S68" s="22"/>
+      <c r="T68" s="22"/>
+      <c r="U68" s="22"/>
+      <c r="V68" s="22"/>
+      <c r="W68" s="22"/>
+      <c r="X68" s="22"/>
+      <c r="Y68" s="22"/>
+      <c r="Z68" s="22"/>
     </row>
     <row r="69" ht="12.0" customHeight="1">
       <c r="A69" s="14"/>
@@ -11338,7 +11333,7 @@
       <c r="G69" s="6"/>
       <c r="H69" s="10"/>
       <c r="I69" s="10"/>
-      <c r="J69" s="18"/>
+      <c r="J69" s="17"/>
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
       <c r="M69" s="6"/>
@@ -11357,1260 +11352,1260 @@
       <c r="Z69" s="10"/>
     </row>
     <row r="70" ht="12.0" customHeight="1">
-      <c r="A70" s="23" t="s">
+      <c r="A70" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B70" s="23"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="26"/>
+      <c r="K70" s="22"/>
+      <c r="L70" s="22"/>
+      <c r="M70" s="22"/>
+      <c r="N70" s="22"/>
+      <c r="O70" s="22"/>
+      <c r="P70" s="22"/>
+      <c r="Q70" s="22"/>
+      <c r="R70" s="22"/>
+      <c r="S70" s="22"/>
+      <c r="T70" s="22"/>
+      <c r="U70" s="22"/>
+      <c r="V70" s="22"/>
+      <c r="W70" s="22"/>
+      <c r="X70" s="22"/>
+      <c r="Y70" s="22"/>
+      <c r="Z70" s="22"/>
+    </row>
+    <row r="71" ht="12.0" customHeight="1">
+      <c r="A71" s="23"/>
+      <c r="B71" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="26"/>
+      <c r="K71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
+      <c r="P71" s="22"/>
+      <c r="Q71" s="22"/>
+      <c r="R71" s="22"/>
+      <c r="S71" s="22"/>
+      <c r="T71" s="22"/>
+      <c r="U71" s="22"/>
+      <c r="V71" s="22"/>
+      <c r="W71" s="22"/>
+      <c r="X71" s="22"/>
+      <c r="Y71" s="22"/>
+      <c r="Z71" s="22"/>
+    </row>
+    <row r="72" ht="12.0" customHeight="1">
+      <c r="A72" s="23"/>
+      <c r="B72" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="26"/>
+      <c r="K72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
+      <c r="P72" s="22"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="22"/>
+      <c r="S72" s="22"/>
+      <c r="T72" s="22"/>
+      <c r="U72" s="22"/>
+      <c r="V72" s="22"/>
+      <c r="W72" s="22"/>
+      <c r="X72" s="22"/>
+      <c r="Y72" s="22"/>
+      <c r="Z72" s="22"/>
+    </row>
+    <row r="73" ht="12.0" customHeight="1">
+      <c r="A73" s="23"/>
+      <c r="B73" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="26"/>
+      <c r="K73" s="22"/>
+      <c r="L73" s="22"/>
+      <c r="M73" s="22"/>
+      <c r="N73" s="22"/>
+      <c r="O73" s="22"/>
+      <c r="P73" s="22"/>
+      <c r="Q73" s="22"/>
+      <c r="R73" s="22"/>
+      <c r="S73" s="22"/>
+      <c r="T73" s="22"/>
+      <c r="U73" s="22"/>
+      <c r="V73" s="22"/>
+      <c r="W73" s="22"/>
+      <c r="X73" s="22"/>
+      <c r="Y73" s="22"/>
+      <c r="Z73" s="22"/>
+    </row>
+    <row r="74" ht="12.0" customHeight="1">
+      <c r="A74" s="23"/>
+      <c r="B74" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" s="24"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="26"/>
+      <c r="K74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="T74" s="22"/>
+      <c r="U74" s="22"/>
+      <c r="V74" s="22"/>
+      <c r="W74" s="22"/>
+      <c r="X74" s="22"/>
+      <c r="Y74" s="22"/>
+      <c r="Z74" s="22"/>
+    </row>
+    <row r="75" ht="12.0" customHeight="1">
+      <c r="A75" s="23"/>
+      <c r="B75" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="26"/>
+      <c r="K75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="22"/>
+      <c r="P75" s="22"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="22"/>
+      <c r="S75" s="22"/>
+      <c r="T75" s="22"/>
+      <c r="U75" s="22"/>
+      <c r="V75" s="22"/>
+      <c r="W75" s="22"/>
+      <c r="X75" s="22"/>
+      <c r="Y75" s="22"/>
+      <c r="Z75" s="22"/>
+    </row>
+    <row r="76" ht="12.0" customHeight="1">
+      <c r="A76" s="23"/>
+      <c r="B76" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C76" s="28">
+        <v>-1.0E20</v>
+      </c>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="22"/>
+      <c r="I76" s="22"/>
+      <c r="J76" s="26"/>
+      <c r="K76" s="22"/>
+      <c r="L76" s="22"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="22"/>
+      <c r="P76" s="22"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="22"/>
+      <c r="S76" s="22"/>
+      <c r="T76" s="22"/>
+      <c r="U76" s="22"/>
+      <c r="V76" s="22"/>
+      <c r="W76" s="22"/>
+      <c r="X76" s="22"/>
+      <c r="Y76" s="22"/>
+      <c r="Z76" s="22"/>
+    </row>
+    <row r="77" ht="12.0" customHeight="1">
+      <c r="A77" s="23"/>
+      <c r="B77" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D77" s="22"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="22"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="22"/>
+      <c r="I77" s="22"/>
+      <c r="J77" s="26"/>
+      <c r="K77" s="22"/>
+      <c r="L77" s="22"/>
+      <c r="M77" s="22"/>
+      <c r="N77" s="22"/>
+      <c r="O77" s="22"/>
+      <c r="P77" s="22"/>
+      <c r="Q77" s="22"/>
+      <c r="R77" s="22"/>
+      <c r="S77" s="22"/>
+      <c r="T77" s="22"/>
+      <c r="U77" s="22"/>
+      <c r="V77" s="22"/>
+      <c r="W77" s="22"/>
+      <c r="X77" s="22"/>
+      <c r="Y77" s="22"/>
+      <c r="Z77" s="22"/>
+    </row>
+    <row r="78" ht="12.0" customHeight="1">
+      <c r="A78" s="23"/>
+      <c r="B78" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C78" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="F78" s="22"/>
+      <c r="G78" s="22"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="22"/>
+      <c r="J78" s="26"/>
+      <c r="K78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="22"/>
+      <c r="P78" s="22"/>
+      <c r="Q78" s="22"/>
+      <c r="R78" s="22"/>
+      <c r="S78" s="22"/>
+      <c r="T78" s="22"/>
+      <c r="U78" s="22"/>
+      <c r="V78" s="22"/>
+      <c r="W78" s="22"/>
+      <c r="X78" s="22"/>
+      <c r="Y78" s="22"/>
+      <c r="Z78" s="22"/>
+    </row>
+    <row r="79" ht="12.0" customHeight="1">
+      <c r="A79" s="23"/>
+      <c r="B79" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C79" s="26"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="26"/>
+      <c r="K79" s="22"/>
+      <c r="L79" s="22"/>
+      <c r="M79" s="22"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="22"/>
+      <c r="P79" s="22"/>
+      <c r="Q79" s="22"/>
+      <c r="R79" s="22"/>
+      <c r="S79" s="22"/>
+      <c r="T79" s="22"/>
+      <c r="U79" s="22"/>
+      <c r="V79" s="22"/>
+      <c r="W79" s="22"/>
+      <c r="X79" s="22"/>
+      <c r="Y79" s="22"/>
+      <c r="Z79" s="22"/>
+    </row>
+    <row r="80" ht="12.0" customHeight="1">
+      <c r="A80" s="23"/>
+      <c r="B80" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C80" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D80" s="22"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="22"/>
+      <c r="G80" s="22"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="22"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="22"/>
+      <c r="L80" s="22"/>
+      <c r="M80" s="22"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="22"/>
+      <c r="P80" s="22"/>
+      <c r="Q80" s="22"/>
+      <c r="R80" s="22"/>
+      <c r="S80" s="22"/>
+      <c r="T80" s="22"/>
+      <c r="U80" s="22"/>
+      <c r="V80" s="22"/>
+      <c r="W80" s="22"/>
+      <c r="X80" s="22"/>
+      <c r="Y80" s="22"/>
+      <c r="Z80" s="22"/>
+    </row>
+    <row r="81" ht="12.0" customHeight="1">
+      <c r="A81" s="23"/>
+      <c r="B81" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C81" s="27"/>
+      <c r="D81" s="22"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="22"/>
+      <c r="G81" s="22"/>
+      <c r="H81" s="22"/>
+      <c r="I81" s="22"/>
+      <c r="J81" s="26"/>
+      <c r="K81" s="22"/>
+      <c r="L81" s="22"/>
+      <c r="M81" s="22"/>
+      <c r="N81" s="22"/>
+      <c r="O81" s="22"/>
+      <c r="P81" s="22"/>
+      <c r="Q81" s="22"/>
+      <c r="R81" s="22"/>
+      <c r="S81" s="22"/>
+      <c r="T81" s="22"/>
+      <c r="U81" s="22"/>
+      <c r="V81" s="22"/>
+      <c r="W81" s="22"/>
+      <c r="X81" s="22"/>
+      <c r="Y81" s="22"/>
+      <c r="Z81" s="22"/>
+    </row>
+    <row r="82" ht="12.0" customHeight="1">
+      <c r="A82" s="23"/>
+      <c r="B82" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C82" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B70" s="24"/>
-      <c r="C70" s="25"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="28"/>
-      <c r="K70" s="27"/>
-      <c r="L70" s="27"/>
-      <c r="M70" s="27"/>
-      <c r="N70" s="27"/>
-      <c r="O70" s="27"/>
-      <c r="P70" s="27"/>
-      <c r="Q70" s="27"/>
-      <c r="R70" s="27"/>
-      <c r="S70" s="27"/>
-      <c r="T70" s="27"/>
-      <c r="U70" s="27"/>
-      <c r="V70" s="27"/>
-      <c r="W70" s="27"/>
-      <c r="X70" s="27"/>
-      <c r="Y70" s="27"/>
-      <c r="Z70" s="27"/>
-    </row>
-    <row r="71" ht="12.0" customHeight="1">
-      <c r="A71" s="24"/>
-      <c r="B71" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C71" s="28" t="s">
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="22"/>
+      <c r="G82" s="22"/>
+      <c r="H82" s="22"/>
+      <c r="I82" s="22"/>
+      <c r="J82" s="26"/>
+      <c r="K82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="22"/>
+      <c r="P82" s="22"/>
+      <c r="Q82" s="22"/>
+      <c r="R82" s="22"/>
+      <c r="S82" s="22"/>
+      <c r="T82" s="22"/>
+      <c r="U82" s="22"/>
+      <c r="V82" s="22"/>
+      <c r="W82" s="22"/>
+      <c r="X82" s="22"/>
+      <c r="Y82" s="22"/>
+      <c r="Z82" s="22"/>
+    </row>
+    <row r="83" ht="12.0" customHeight="1">
+      <c r="A83" s="23"/>
+      <c r="B83" s="22"/>
+      <c r="C83" s="27"/>
+      <c r="D83" s="22"/>
+      <c r="E83" s="22"/>
+      <c r="F83" s="22"/>
+      <c r="G83" s="22"/>
+      <c r="H83" s="22"/>
+      <c r="I83" s="22"/>
+      <c r="J83" s="26"/>
+      <c r="K83" s="22"/>
+      <c r="L83" s="22"/>
+      <c r="M83" s="22"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="22"/>
+      <c r="P83" s="22"/>
+      <c r="Q83" s="22"/>
+      <c r="R83" s="22"/>
+      <c r="S83" s="22"/>
+      <c r="T83" s="22"/>
+      <c r="U83" s="22"/>
+      <c r="V83" s="22"/>
+      <c r="W83" s="22"/>
+      <c r="X83" s="22"/>
+      <c r="Y83" s="22"/>
+      <c r="Z83" s="22"/>
+    </row>
+    <row r="84" ht="12.0" customHeight="1">
+      <c r="A84" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B84" s="23"/>
+      <c r="C84" s="24"/>
+      <c r="D84" s="22"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="22"/>
+      <c r="G84" s="22"/>
+      <c r="H84" s="22"/>
+      <c r="I84" s="22"/>
+      <c r="J84" s="26"/>
+      <c r="K84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="22"/>
+      <c r="P84" s="22"/>
+      <c r="Q84" s="22"/>
+      <c r="R84" s="22"/>
+      <c r="S84" s="22"/>
+      <c r="T84" s="22"/>
+      <c r="U84" s="22"/>
+      <c r="V84" s="22"/>
+      <c r="W84" s="22"/>
+      <c r="X84" s="22"/>
+      <c r="Y84" s="22"/>
+      <c r="Z84" s="22"/>
+    </row>
+    <row r="85" ht="12.0" customHeight="1">
+      <c r="A85" s="23"/>
+      <c r="B85" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D71" s="27"/>
-      <c r="E71" s="27"/>
-      <c r="F71" s="27"/>
-      <c r="G71" s="27"/>
-      <c r="H71" s="27"/>
-      <c r="I71" s="27"/>
-      <c r="J71" s="28"/>
-      <c r="K71" s="27"/>
-      <c r="L71" s="27"/>
-      <c r="M71" s="27"/>
-      <c r="N71" s="27"/>
-      <c r="O71" s="27"/>
-      <c r="P71" s="27"/>
-      <c r="Q71" s="27"/>
-      <c r="R71" s="27"/>
-      <c r="S71" s="27"/>
-      <c r="T71" s="27"/>
-      <c r="U71" s="27"/>
-      <c r="V71" s="27"/>
-      <c r="W71" s="27"/>
-      <c r="X71" s="27"/>
-      <c r="Y71" s="27"/>
-      <c r="Z71" s="27"/>
-    </row>
-    <row r="72" ht="12.0" customHeight="1">
-      <c r="A72" s="24"/>
-      <c r="B72" s="27" t="s">
+      <c r="C85" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C72" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D72" s="27"/>
-      <c r="E72" s="27"/>
-      <c r="F72" s="27"/>
-      <c r="G72" s="27"/>
-      <c r="H72" s="27"/>
-      <c r="I72" s="27"/>
-      <c r="J72" s="28"/>
-      <c r="K72" s="27"/>
-      <c r="L72" s="27"/>
-      <c r="M72" s="27"/>
-      <c r="N72" s="27"/>
-      <c r="O72" s="27"/>
-      <c r="P72" s="27"/>
-      <c r="Q72" s="27"/>
-      <c r="R72" s="27"/>
-      <c r="S72" s="27"/>
-      <c r="T72" s="27"/>
-      <c r="U72" s="27"/>
-      <c r="V72" s="27"/>
-      <c r="W72" s="27"/>
-      <c r="X72" s="27"/>
-      <c r="Y72" s="27"/>
-      <c r="Z72" s="27"/>
-    </row>
-    <row r="73" ht="12.0" customHeight="1">
-      <c r="A73" s="24"/>
-      <c r="B73" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C73" s="28" t="s">
+      <c r="D85" s="22"/>
+      <c r="E85" s="22"/>
+      <c r="F85" s="22"/>
+      <c r="G85" s="22"/>
+      <c r="H85" s="22"/>
+      <c r="I85" s="22"/>
+      <c r="J85" s="26"/>
+      <c r="K85" s="22"/>
+      <c r="L85" s="22"/>
+      <c r="M85" s="22"/>
+      <c r="N85" s="22"/>
+      <c r="O85" s="22"/>
+      <c r="P85" s="22"/>
+      <c r="Q85" s="22"/>
+      <c r="R85" s="22"/>
+      <c r="S85" s="22"/>
+      <c r="T85" s="22"/>
+      <c r="U85" s="22"/>
+      <c r="V85" s="22"/>
+      <c r="W85" s="22"/>
+      <c r="X85" s="22"/>
+      <c r="Y85" s="22"/>
+      <c r="Z85" s="22"/>
+    </row>
+    <row r="86" ht="12.0" customHeight="1">
+      <c r="A86" s="23"/>
+      <c r="B86" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D73" s="27"/>
-      <c r="E73" s="27"/>
-      <c r="F73" s="27"/>
-      <c r="G73" s="27"/>
-      <c r="H73" s="27"/>
-      <c r="I73" s="27"/>
-      <c r="J73" s="28"/>
-      <c r="K73" s="27"/>
-      <c r="L73" s="27"/>
-      <c r="M73" s="27"/>
-      <c r="N73" s="27"/>
-      <c r="O73" s="27"/>
-      <c r="P73" s="27"/>
-      <c r="Q73" s="27"/>
-      <c r="R73" s="27"/>
-      <c r="S73" s="27"/>
-      <c r="T73" s="27"/>
-      <c r="U73" s="27"/>
-      <c r="V73" s="27"/>
-      <c r="W73" s="27"/>
-      <c r="X73" s="27"/>
-      <c r="Y73" s="27"/>
-      <c r="Z73" s="27"/>
-    </row>
-    <row r="74" ht="12.0" customHeight="1">
-      <c r="A74" s="24"/>
-      <c r="B74" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C74" s="25"/>
-      <c r="D74" s="27"/>
-      <c r="E74" s="27"/>
-      <c r="F74" s="27"/>
-      <c r="G74" s="27"/>
-      <c r="H74" s="27"/>
-      <c r="I74" s="27"/>
-      <c r="J74" s="28"/>
-      <c r="K74" s="27"/>
-      <c r="L74" s="27"/>
-      <c r="M74" s="27"/>
-      <c r="N74" s="27"/>
-      <c r="O74" s="27"/>
-      <c r="P74" s="27"/>
-      <c r="Q74" s="27"/>
-      <c r="R74" s="27"/>
-      <c r="S74" s="27"/>
-      <c r="T74" s="27"/>
-      <c r="U74" s="27"/>
-      <c r="V74" s="27"/>
-      <c r="W74" s="27"/>
-      <c r="X74" s="27"/>
-      <c r="Y74" s="27"/>
-      <c r="Z74" s="27"/>
-    </row>
-    <row r="75" ht="12.0" customHeight="1">
-      <c r="A75" s="24"/>
-      <c r="B75" s="27" t="s">
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="F86" s="22"/>
+      <c r="G86" s="22"/>
+      <c r="H86" s="22"/>
+      <c r="I86" s="22"/>
+      <c r="J86" s="26"/>
+      <c r="K86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="22"/>
+      <c r="P86" s="22"/>
+      <c r="Q86" s="22"/>
+      <c r="R86" s="22"/>
+      <c r="S86" s="22"/>
+      <c r="T86" s="22"/>
+      <c r="U86" s="22"/>
+      <c r="V86" s="22"/>
+      <c r="W86" s="22"/>
+      <c r="X86" s="22"/>
+      <c r="Y86" s="22"/>
+      <c r="Z86" s="22"/>
+    </row>
+    <row r="87" ht="12.0" customHeight="1">
+      <c r="A87" s="23"/>
+      <c r="B87" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D87" s="22"/>
+      <c r="E87" s="22"/>
+      <c r="F87" s="22"/>
+      <c r="G87" s="22"/>
+      <c r="H87" s="22"/>
+      <c r="I87" s="22"/>
+      <c r="J87" s="26"/>
+      <c r="K87" s="22"/>
+      <c r="L87" s="22"/>
+      <c r="M87" s="22"/>
+      <c r="N87" s="22"/>
+      <c r="O87" s="22"/>
+      <c r="P87" s="22"/>
+      <c r="Q87" s="22"/>
+      <c r="R87" s="22"/>
+      <c r="S87" s="22"/>
+      <c r="T87" s="22"/>
+      <c r="U87" s="22"/>
+      <c r="V87" s="22"/>
+      <c r="W87" s="22"/>
+      <c r="X87" s="22"/>
+      <c r="Y87" s="22"/>
+      <c r="Z87" s="22"/>
+    </row>
+    <row r="88" ht="12.0" customHeight="1">
+      <c r="A88" s="23"/>
+      <c r="B88" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C75" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="D75" s="27"/>
-      <c r="E75" s="27"/>
-      <c r="F75" s="27"/>
-      <c r="G75" s="27"/>
-      <c r="H75" s="27"/>
-      <c r="I75" s="27"/>
-      <c r="J75" s="28"/>
-      <c r="K75" s="27"/>
-      <c r="L75" s="27"/>
-      <c r="M75" s="27"/>
-      <c r="N75" s="27"/>
-      <c r="O75" s="27"/>
-      <c r="P75" s="27"/>
-      <c r="Q75" s="27"/>
-      <c r="R75" s="27"/>
-      <c r="S75" s="27"/>
-      <c r="T75" s="27"/>
-      <c r="U75" s="27"/>
-      <c r="V75" s="27"/>
-      <c r="W75" s="27"/>
-      <c r="X75" s="27"/>
-      <c r="Y75" s="27"/>
-      <c r="Z75" s="27"/>
-    </row>
-    <row r="76" ht="12.0" customHeight="1">
-      <c r="A76" s="24"/>
-      <c r="B76" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C76" s="31">
+      <c r="C88" s="24"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="F88" s="22"/>
+      <c r="G88" s="22"/>
+      <c r="H88" s="22"/>
+      <c r="I88" s="22"/>
+      <c r="J88" s="26"/>
+      <c r="K88" s="22"/>
+      <c r="L88" s="22"/>
+      <c r="M88" s="22"/>
+      <c r="N88" s="22"/>
+      <c r="O88" s="22"/>
+      <c r="P88" s="22"/>
+      <c r="Q88" s="22"/>
+      <c r="R88" s="22"/>
+      <c r="S88" s="22"/>
+      <c r="T88" s="22"/>
+      <c r="U88" s="22"/>
+      <c r="V88" s="22"/>
+      <c r="W88" s="22"/>
+      <c r="X88" s="22"/>
+      <c r="Y88" s="22"/>
+      <c r="Z88" s="22"/>
+    </row>
+    <row r="89" ht="12.0" customHeight="1">
+      <c r="A89" s="23"/>
+      <c r="B89" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D89" s="22"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="22"/>
+      <c r="H89" s="22"/>
+      <c r="I89" s="22"/>
+      <c r="J89" s="26"/>
+      <c r="K89" s="22"/>
+      <c r="L89" s="22"/>
+      <c r="M89" s="22"/>
+      <c r="N89" s="22"/>
+      <c r="O89" s="22"/>
+      <c r="P89" s="22"/>
+      <c r="Q89" s="22"/>
+      <c r="R89" s="22"/>
+      <c r="S89" s="22"/>
+      <c r="T89" s="22"/>
+      <c r="U89" s="22"/>
+      <c r="V89" s="22"/>
+      <c r="W89" s="22"/>
+      <c r="X89" s="22"/>
+      <c r="Y89" s="22"/>
+      <c r="Z89" s="22"/>
+    </row>
+    <row r="90" ht="12.0" customHeight="1">
+      <c r="A90" s="23"/>
+      <c r="B90" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C90" s="28">
         <v>-1.0E20</v>
       </c>
-      <c r="D76" s="27"/>
-      <c r="E76" s="27"/>
-      <c r="F76" s="27"/>
-      <c r="G76" s="27"/>
-      <c r="H76" s="27"/>
-      <c r="I76" s="27"/>
-      <c r="J76" s="28"/>
-      <c r="K76" s="27"/>
-      <c r="L76" s="27"/>
-      <c r="M76" s="27"/>
-      <c r="N76" s="27"/>
-      <c r="O76" s="27"/>
-      <c r="P76" s="27"/>
-      <c r="Q76" s="27"/>
-      <c r="R76" s="27"/>
-      <c r="S76" s="27"/>
-      <c r="T76" s="27"/>
-      <c r="U76" s="27"/>
-      <c r="V76" s="27"/>
-      <c r="W76" s="27"/>
-      <c r="X76" s="27"/>
-      <c r="Y76" s="27"/>
-      <c r="Z76" s="27"/>
-    </row>
-    <row r="77" ht="12.0" customHeight="1">
-      <c r="A77" s="24"/>
-      <c r="B77" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C77" s="32" t="s">
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="F90" s="22"/>
+      <c r="G90" s="22"/>
+      <c r="H90" s="22"/>
+      <c r="I90" s="22"/>
+      <c r="J90" s="26"/>
+      <c r="K90" s="22"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="22"/>
+      <c r="O90" s="22"/>
+      <c r="P90" s="22"/>
+      <c r="Q90" s="22"/>
+      <c r="R90" s="22"/>
+      <c r="S90" s="22"/>
+      <c r="T90" s="22"/>
+      <c r="U90" s="22"/>
+      <c r="V90" s="22"/>
+      <c r="W90" s="22"/>
+      <c r="X90" s="22"/>
+      <c r="Y90" s="22"/>
+      <c r="Z90" s="22"/>
+    </row>
+    <row r="91" ht="12.0" customHeight="1">
+      <c r="A91" s="23"/>
+      <c r="B91" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D77" s="27"/>
-      <c r="E77" s="27"/>
-      <c r="F77" s="27"/>
-      <c r="G77" s="27"/>
-      <c r="H77" s="27"/>
-      <c r="I77" s="27"/>
-      <c r="J77" s="28"/>
-      <c r="K77" s="27"/>
-      <c r="L77" s="27"/>
-      <c r="M77" s="27"/>
-      <c r="N77" s="27"/>
-      <c r="O77" s="27"/>
-      <c r="P77" s="27"/>
-      <c r="Q77" s="27"/>
-      <c r="R77" s="27"/>
-      <c r="S77" s="27"/>
-      <c r="T77" s="27"/>
-      <c r="U77" s="27"/>
-      <c r="V77" s="27"/>
-      <c r="W77" s="27"/>
-      <c r="X77" s="27"/>
-      <c r="Y77" s="27"/>
-      <c r="Z77" s="27"/>
-    </row>
-    <row r="78" ht="12.0" customHeight="1">
-      <c r="A78" s="24"/>
-      <c r="B78" s="27" t="s">
+      <c r="C91" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="C78" s="32" t="s">
+      <c r="D91" s="22"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="22"/>
+      <c r="G91" s="22"/>
+      <c r="H91" s="22"/>
+      <c r="I91" s="22"/>
+      <c r="J91" s="26"/>
+      <c r="K91" s="22"/>
+      <c r="L91" s="22"/>
+      <c r="M91" s="22"/>
+      <c r="N91" s="22"/>
+      <c r="O91" s="22"/>
+      <c r="P91" s="22"/>
+      <c r="Q91" s="22"/>
+      <c r="R91" s="22"/>
+      <c r="S91" s="22"/>
+      <c r="T91" s="22"/>
+      <c r="U91" s="22"/>
+      <c r="V91" s="22"/>
+      <c r="W91" s="22"/>
+      <c r="X91" s="22"/>
+      <c r="Y91" s="22"/>
+      <c r="Z91" s="22"/>
+    </row>
+    <row r="92" ht="12.0" customHeight="1">
+      <c r="A92" s="23"/>
+      <c r="B92" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C92" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D92" s="22"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
+      <c r="G92" s="22"/>
+      <c r="H92" s="22"/>
+      <c r="I92" s="22"/>
+      <c r="J92" s="26"/>
+      <c r="K92" s="22"/>
+      <c r="L92" s="22"/>
+      <c r="M92" s="22"/>
+      <c r="N92" s="22"/>
+      <c r="O92" s="22"/>
+      <c r="P92" s="22"/>
+      <c r="Q92" s="22"/>
+      <c r="R92" s="22"/>
+      <c r="S92" s="22"/>
+      <c r="T92" s="22"/>
+      <c r="U92" s="22"/>
+      <c r="V92" s="22"/>
+      <c r="W92" s="22"/>
+      <c r="X92" s="22"/>
+      <c r="Y92" s="22"/>
+      <c r="Z92" s="22"/>
+    </row>
+    <row r="93" ht="12.0" customHeight="1">
+      <c r="A93" s="23"/>
+      <c r="B93" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C93" s="26"/>
+      <c r="D93" s="22"/>
+      <c r="E93" s="22"/>
+      <c r="F93" s="22"/>
+      <c r="G93" s="22"/>
+      <c r="H93" s="22"/>
+      <c r="I93" s="22"/>
+      <c r="J93" s="26"/>
+      <c r="K93" s="22"/>
+      <c r="L93" s="22"/>
+      <c r="M93" s="22"/>
+      <c r="N93" s="22"/>
+      <c r="O93" s="22"/>
+      <c r="P93" s="22"/>
+      <c r="Q93" s="22"/>
+      <c r="R93" s="22"/>
+      <c r="S93" s="22"/>
+      <c r="T93" s="22"/>
+      <c r="U93" s="22"/>
+      <c r="V93" s="22"/>
+      <c r="W93" s="22"/>
+      <c r="X93" s="22"/>
+      <c r="Y93" s="22"/>
+      <c r="Z93" s="22"/>
+    </row>
+    <row r="94" ht="12.0" customHeight="1">
+      <c r="A94" s="23"/>
+      <c r="B94" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C94" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D94" s="22"/>
+      <c r="E94" s="22"/>
+      <c r="F94" s="22"/>
+      <c r="G94" s="22"/>
+      <c r="H94" s="22"/>
+      <c r="I94" s="22"/>
+      <c r="J94" s="26"/>
+      <c r="K94" s="22"/>
+      <c r="L94" s="22"/>
+      <c r="M94" s="22"/>
+      <c r="N94" s="22"/>
+      <c r="O94" s="22"/>
+      <c r="P94" s="22"/>
+      <c r="Q94" s="22"/>
+      <c r="R94" s="22"/>
+      <c r="S94" s="22"/>
+      <c r="T94" s="22"/>
+      <c r="U94" s="22"/>
+      <c r="V94" s="22"/>
+      <c r="W94" s="22"/>
+      <c r="X94" s="22"/>
+      <c r="Y94" s="22"/>
+      <c r="Z94" s="22"/>
+    </row>
+    <row r="95" ht="12.0" customHeight="1">
+      <c r="A95" s="23"/>
+      <c r="B95" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C95" s="27"/>
+      <c r="D95" s="22"/>
+      <c r="E95" s="22"/>
+      <c r="F95" s="22"/>
+      <c r="G95" s="22"/>
+      <c r="H95" s="22"/>
+      <c r="I95" s="22"/>
+      <c r="J95" s="26"/>
+      <c r="K95" s="22"/>
+      <c r="L95" s="22"/>
+      <c r="M95" s="22"/>
+      <c r="N95" s="22"/>
+      <c r="O95" s="22"/>
+      <c r="P95" s="22"/>
+      <c r="Q95" s="22"/>
+      <c r="R95" s="22"/>
+      <c r="S95" s="22"/>
+      <c r="T95" s="22"/>
+      <c r="U95" s="22"/>
+      <c r="V95" s="22"/>
+      <c r="W95" s="22"/>
+      <c r="X95" s="22"/>
+      <c r="Y95" s="22"/>
+      <c r="Z95" s="22"/>
+    </row>
+    <row r="96" ht="12.0" customHeight="1">
+      <c r="A96" s="23"/>
+      <c r="B96" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C96" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D96" s="22"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="22"/>
+      <c r="G96" s="22"/>
+      <c r="H96" s="22"/>
+      <c r="I96" s="22"/>
+      <c r="J96" s="26"/>
+      <c r="K96" s="22"/>
+      <c r="L96" s="22"/>
+      <c r="M96" s="22"/>
+      <c r="N96" s="22"/>
+      <c r="O96" s="22"/>
+      <c r="P96" s="22"/>
+      <c r="Q96" s="22"/>
+      <c r="R96" s="22"/>
+      <c r="S96" s="22"/>
+      <c r="T96" s="22"/>
+      <c r="U96" s="22"/>
+      <c r="V96" s="22"/>
+      <c r="W96" s="22"/>
+      <c r="X96" s="22"/>
+      <c r="Y96" s="22"/>
+      <c r="Z96" s="22"/>
+    </row>
+    <row r="97" ht="12.0" customHeight="1">
+      <c r="A97" s="23"/>
+      <c r="B97" s="22"/>
+      <c r="C97" s="27"/>
+      <c r="D97" s="22"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="22"/>
+      <c r="G97" s="22"/>
+      <c r="H97" s="22"/>
+      <c r="I97" s="22"/>
+      <c r="J97" s="26"/>
+      <c r="K97" s="22"/>
+      <c r="L97" s="22"/>
+      <c r="M97" s="22"/>
+      <c r="N97" s="22"/>
+      <c r="O97" s="22"/>
+      <c r="P97" s="22"/>
+      <c r="Q97" s="22"/>
+      <c r="R97" s="22"/>
+      <c r="S97" s="22"/>
+      <c r="T97" s="22"/>
+      <c r="U97" s="22"/>
+      <c r="V97" s="22"/>
+      <c r="W97" s="22"/>
+      <c r="X97" s="22"/>
+      <c r="Y97" s="22"/>
+      <c r="Z97" s="22"/>
+    </row>
+    <row r="98" ht="12.0" customHeight="1">
+      <c r="A98" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B98" s="23"/>
+      <c r="C98" s="24"/>
+      <c r="D98" s="22"/>
+      <c r="E98" s="22"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="22"/>
+      <c r="H98" s="22"/>
+      <c r="I98" s="22"/>
+      <c r="J98" s="26"/>
+      <c r="K98" s="22"/>
+      <c r="L98" s="22"/>
+      <c r="M98" s="22"/>
+      <c r="N98" s="22"/>
+      <c r="O98" s="22"/>
+      <c r="P98" s="22"/>
+      <c r="Q98" s="22"/>
+      <c r="R98" s="22"/>
+      <c r="S98" s="22"/>
+      <c r="T98" s="22"/>
+      <c r="U98" s="22"/>
+      <c r="V98" s="22"/>
+      <c r="W98" s="22"/>
+      <c r="X98" s="22"/>
+      <c r="Y98" s="22"/>
+      <c r="Z98" s="22"/>
+    </row>
+    <row r="99" ht="12.0" customHeight="1">
+      <c r="A99" s="23"/>
+      <c r="B99" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D99" s="22"/>
+      <c r="E99" s="22"/>
+      <c r="F99" s="22"/>
+      <c r="G99" s="22"/>
+      <c r="H99" s="22"/>
+      <c r="I99" s="22"/>
+      <c r="J99" s="26"/>
+      <c r="K99" s="22"/>
+      <c r="L99" s="22"/>
+      <c r="M99" s="22"/>
+      <c r="N99" s="22"/>
+      <c r="O99" s="22"/>
+      <c r="P99" s="22"/>
+      <c r="Q99" s="22"/>
+      <c r="R99" s="22"/>
+      <c r="S99" s="22"/>
+      <c r="T99" s="22"/>
+      <c r="U99" s="22"/>
+      <c r="V99" s="22"/>
+      <c r="W99" s="22"/>
+      <c r="X99" s="22"/>
+      <c r="Y99" s="22"/>
+      <c r="Z99" s="22"/>
+    </row>
+    <row r="100" ht="12.0" customHeight="1">
+      <c r="A100" s="23"/>
+      <c r="B100" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C100" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D100" s="22"/>
+      <c r="E100" s="22"/>
+      <c r="F100" s="22"/>
+      <c r="G100" s="22"/>
+      <c r="H100" s="22"/>
+      <c r="I100" s="22"/>
+      <c r="J100" s="26"/>
+      <c r="K100" s="22"/>
+      <c r="L100" s="22"/>
+      <c r="M100" s="22"/>
+      <c r="N100" s="22"/>
+      <c r="O100" s="22"/>
+      <c r="P100" s="22"/>
+      <c r="Q100" s="22"/>
+      <c r="R100" s="22"/>
+      <c r="S100" s="22"/>
+      <c r="T100" s="22"/>
+      <c r="U100" s="22"/>
+      <c r="V100" s="22"/>
+      <c r="W100" s="22"/>
+      <c r="X100" s="22"/>
+      <c r="Y100" s="22"/>
+      <c r="Z100" s="22"/>
+    </row>
+    <row r="101" ht="12.0" customHeight="1">
+      <c r="A101" s="23"/>
+      <c r="B101" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D101" s="22"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="22"/>
+      <c r="G101" s="22"/>
+      <c r="H101" s="22"/>
+      <c r="I101" s="22"/>
+      <c r="J101" s="26"/>
+      <c r="K101" s="22"/>
+      <c r="L101" s="22"/>
+      <c r="M101" s="22"/>
+      <c r="N101" s="22"/>
+      <c r="O101" s="22"/>
+      <c r="P101" s="22"/>
+      <c r="Q101" s="22"/>
+      <c r="R101" s="22"/>
+      <c r="S101" s="22"/>
+      <c r="T101" s="22"/>
+      <c r="U101" s="22"/>
+      <c r="V101" s="22"/>
+      <c r="W101" s="22"/>
+      <c r="X101" s="22"/>
+      <c r="Y101" s="22"/>
+      <c r="Z101" s="22"/>
+    </row>
+    <row r="102" ht="12.0" customHeight="1">
+      <c r="A102" s="23"/>
+      <c r="B102" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C102" s="24"/>
+      <c r="D102" s="22"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="22"/>
+      <c r="H102" s="22"/>
+      <c r="I102" s="22"/>
+      <c r="J102" s="26"/>
+      <c r="K102" s="22"/>
+      <c r="L102" s="22"/>
+      <c r="M102" s="22"/>
+      <c r="N102" s="22"/>
+      <c r="O102" s="22"/>
+      <c r="P102" s="22"/>
+      <c r="Q102" s="22"/>
+      <c r="R102" s="22"/>
+      <c r="S102" s="22"/>
+      <c r="T102" s="22"/>
+      <c r="U102" s="22"/>
+      <c r="V102" s="22"/>
+      <c r="W102" s="22"/>
+      <c r="X102" s="22"/>
+      <c r="Y102" s="22"/>
+      <c r="Z102" s="22"/>
+    </row>
+    <row r="103" ht="12.0" customHeight="1">
+      <c r="A103" s="23"/>
+      <c r="B103" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C103" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="D103" s="22"/>
+      <c r="E103" s="22"/>
+      <c r="F103" s="22"/>
+      <c r="G103" s="22"/>
+      <c r="H103" s="22"/>
+      <c r="I103" s="22"/>
+      <c r="J103" s="26"/>
+      <c r="K103" s="22"/>
+      <c r="L103" s="22"/>
+      <c r="M103" s="22"/>
+      <c r="N103" s="22"/>
+      <c r="O103" s="22"/>
+      <c r="P103" s="22"/>
+      <c r="Q103" s="22"/>
+      <c r="R103" s="22"/>
+      <c r="S103" s="22"/>
+      <c r="T103" s="22"/>
+      <c r="U103" s="22"/>
+      <c r="V103" s="22"/>
+      <c r="W103" s="22"/>
+      <c r="X103" s="22"/>
+      <c r="Y103" s="22"/>
+      <c r="Z103" s="22"/>
+    </row>
+    <row r="104" ht="12.0" customHeight="1">
+      <c r="A104" s="23"/>
+      <c r="B104" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C104" s="28">
+        <v>-1.0E20</v>
+      </c>
+      <c r="D104" s="22"/>
+      <c r="E104" s="22"/>
+      <c r="F104" s="22"/>
+      <c r="G104" s="22"/>
+      <c r="H104" s="22"/>
+      <c r="I104" s="22"/>
+      <c r="J104" s="26"/>
+      <c r="K104" s="22"/>
+      <c r="L104" s="22"/>
+      <c r="M104" s="22"/>
+      <c r="N104" s="22"/>
+      <c r="O104" s="22"/>
+      <c r="P104" s="22"/>
+      <c r="Q104" s="22"/>
+      <c r="R104" s="22"/>
+      <c r="S104" s="22"/>
+      <c r="T104" s="22"/>
+      <c r="U104" s="22"/>
+      <c r="V104" s="22"/>
+      <c r="W104" s="22"/>
+      <c r="X104" s="22"/>
+      <c r="Y104" s="22"/>
+      <c r="Z104" s="22"/>
+    </row>
+    <row r="105" ht="12.0" customHeight="1">
+      <c r="A105" s="23"/>
+      <c r="B105" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="27"/>
-      <c r="H78" s="27"/>
-      <c r="I78" s="27"/>
-      <c r="J78" s="28"/>
-      <c r="K78" s="27"/>
-      <c r="L78" s="27"/>
-      <c r="M78" s="27"/>
-      <c r="N78" s="27"/>
-      <c r="O78" s="27"/>
-      <c r="P78" s="27"/>
-      <c r="Q78" s="27"/>
-      <c r="R78" s="27"/>
-      <c r="S78" s="27"/>
-      <c r="T78" s="27"/>
-      <c r="U78" s="27"/>
-      <c r="V78" s="27"/>
-      <c r="W78" s="27"/>
-      <c r="X78" s="27"/>
-      <c r="Y78" s="27"/>
-      <c r="Z78" s="27"/>
-    </row>
-    <row r="79" ht="12.0" customHeight="1">
-      <c r="A79" s="24"/>
-      <c r="B79" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C79" s="28"/>
-      <c r="D79" s="27"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="27"/>
-      <c r="H79" s="27"/>
-      <c r="I79" s="27"/>
-      <c r="J79" s="28"/>
-      <c r="K79" s="27"/>
-      <c r="L79" s="27"/>
-      <c r="M79" s="27"/>
-      <c r="N79" s="27"/>
-      <c r="O79" s="27"/>
-      <c r="P79" s="27"/>
-      <c r="Q79" s="27"/>
-      <c r="R79" s="27"/>
-      <c r="S79" s="27"/>
-      <c r="T79" s="27"/>
-      <c r="U79" s="27"/>
-      <c r="V79" s="27"/>
-      <c r="W79" s="27"/>
-      <c r="X79" s="27"/>
-      <c r="Y79" s="27"/>
-      <c r="Z79" s="27"/>
-    </row>
-    <row r="80" ht="12.0" customHeight="1">
-      <c r="A80" s="24"/>
-      <c r="B80" s="27" t="s">
+      <c r="C105" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D105" s="22"/>
+      <c r="E105" s="22"/>
+      <c r="F105" s="22"/>
+      <c r="G105" s="22"/>
+      <c r="H105" s="22"/>
+      <c r="I105" s="22"/>
+      <c r="J105" s="26"/>
+      <c r="K105" s="22"/>
+      <c r="L105" s="22"/>
+      <c r="M105" s="22"/>
+      <c r="N105" s="22"/>
+      <c r="O105" s="22"/>
+      <c r="P105" s="22"/>
+      <c r="Q105" s="22"/>
+      <c r="R105" s="22"/>
+      <c r="S105" s="22"/>
+      <c r="T105" s="22"/>
+      <c r="U105" s="22"/>
+      <c r="V105" s="22"/>
+      <c r="W105" s="22"/>
+      <c r="X105" s="22"/>
+      <c r="Y105" s="22"/>
+      <c r="Z105" s="22"/>
+    </row>
+    <row r="106" ht="12.0" customHeight="1">
+      <c r="A106" s="23"/>
+      <c r="B106" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C80" s="29" t="s">
+      <c r="C106" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D106" s="22"/>
+      <c r="E106" s="22"/>
+      <c r="F106" s="22"/>
+      <c r="G106" s="22"/>
+      <c r="H106" s="22"/>
+      <c r="I106" s="22"/>
+      <c r="J106" s="26"/>
+      <c r="K106" s="22"/>
+      <c r="L106" s="22"/>
+      <c r="M106" s="22"/>
+      <c r="N106" s="22"/>
+      <c r="O106" s="22"/>
+      <c r="P106" s="22"/>
+      <c r="Q106" s="22"/>
+      <c r="R106" s="22"/>
+      <c r="S106" s="22"/>
+      <c r="T106" s="22"/>
+      <c r="U106" s="22"/>
+      <c r="V106" s="22"/>
+      <c r="W106" s="22"/>
+      <c r="X106" s="22"/>
+      <c r="Y106" s="22"/>
+      <c r="Z106" s="22"/>
+    </row>
+    <row r="107" ht="12.0" customHeight="1">
+      <c r="A107" s="23"/>
+      <c r="B107" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C107" s="26"/>
+      <c r="D107" s="22"/>
+      <c r="E107" s="22"/>
+      <c r="F107" s="22"/>
+      <c r="G107" s="22"/>
+      <c r="H107" s="22"/>
+      <c r="I107" s="22"/>
+      <c r="J107" s="26"/>
+      <c r="K107" s="22"/>
+      <c r="L107" s="22"/>
+      <c r="M107" s="22"/>
+      <c r="N107" s="22"/>
+      <c r="O107" s="22"/>
+      <c r="P107" s="22"/>
+      <c r="Q107" s="22"/>
+      <c r="R107" s="22"/>
+      <c r="S107" s="22"/>
+      <c r="T107" s="22"/>
+      <c r="U107" s="22"/>
+      <c r="V107" s="22"/>
+      <c r="W107" s="22"/>
+      <c r="X107" s="22"/>
+      <c r="Y107" s="22"/>
+      <c r="Z107" s="22"/>
+    </row>
+    <row r="108" ht="12.0" customHeight="1">
+      <c r="A108" s="23"/>
+      <c r="B108" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D80" s="27"/>
-      <c r="E80" s="27"/>
-      <c r="F80" s="27"/>
-      <c r="G80" s="27"/>
-      <c r="H80" s="27"/>
-      <c r="I80" s="27"/>
-      <c r="J80" s="28"/>
-      <c r="K80" s="27"/>
-      <c r="L80" s="27"/>
-      <c r="M80" s="27"/>
-      <c r="N80" s="27"/>
-      <c r="O80" s="27"/>
-      <c r="P80" s="27"/>
-      <c r="Q80" s="27"/>
-      <c r="R80" s="27"/>
-      <c r="S80" s="27"/>
-      <c r="T80" s="27"/>
-      <c r="U80" s="27"/>
-      <c r="V80" s="27"/>
-      <c r="W80" s="27"/>
-      <c r="X80" s="27"/>
-      <c r="Y80" s="27"/>
-      <c r="Z80" s="27"/>
-    </row>
-    <row r="81" ht="12.0" customHeight="1">
-      <c r="A81" s="24"/>
-      <c r="B81" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C81" s="29"/>
-      <c r="D81" s="27"/>
-      <c r="E81" s="27"/>
-      <c r="F81" s="27"/>
-      <c r="G81" s="27"/>
-      <c r="H81" s="27"/>
-      <c r="I81" s="27"/>
-      <c r="J81" s="28"/>
-      <c r="K81" s="27"/>
-      <c r="L81" s="27"/>
-      <c r="M81" s="27"/>
-      <c r="N81" s="27"/>
-      <c r="O81" s="27"/>
-      <c r="P81" s="27"/>
-      <c r="Q81" s="27"/>
-      <c r="R81" s="27"/>
-      <c r="S81" s="27"/>
-      <c r="T81" s="27"/>
-      <c r="U81" s="27"/>
-      <c r="V81" s="27"/>
-      <c r="W81" s="27"/>
-      <c r="X81" s="27"/>
-      <c r="Y81" s="27"/>
-      <c r="Z81" s="27"/>
-    </row>
-    <row r="82" ht="12.0" customHeight="1">
-      <c r="A82" s="24"/>
-      <c r="B82" s="27" t="s">
+      <c r="C108" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D108" s="22"/>
+      <c r="E108" s="22"/>
+      <c r="F108" s="22"/>
+      <c r="G108" s="22"/>
+      <c r="H108" s="22"/>
+      <c r="I108" s="22"/>
+      <c r="J108" s="26"/>
+      <c r="K108" s="22"/>
+      <c r="L108" s="22"/>
+      <c r="M108" s="22"/>
+      <c r="N108" s="22"/>
+      <c r="O108" s="22"/>
+      <c r="P108" s="22"/>
+      <c r="Q108" s="22"/>
+      <c r="R108" s="22"/>
+      <c r="S108" s="22"/>
+      <c r="T108" s="22"/>
+      <c r="U108" s="22"/>
+      <c r="V108" s="22"/>
+      <c r="W108" s="22"/>
+      <c r="X108" s="22"/>
+      <c r="Y108" s="22"/>
+      <c r="Z108" s="22"/>
+    </row>
+    <row r="109" ht="12.0" customHeight="1">
+      <c r="A109" s="23"/>
+      <c r="B109" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="C82" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="D82" s="27"/>
-      <c r="E82" s="27"/>
-      <c r="F82" s="27"/>
-      <c r="G82" s="27"/>
-      <c r="H82" s="27"/>
-      <c r="I82" s="27"/>
-      <c r="J82" s="28"/>
-      <c r="K82" s="27"/>
-      <c r="L82" s="27"/>
-      <c r="M82" s="27"/>
-      <c r="N82" s="27"/>
-      <c r="O82" s="27"/>
-      <c r="P82" s="27"/>
-      <c r="Q82" s="27"/>
-      <c r="R82" s="27"/>
-      <c r="S82" s="27"/>
-      <c r="T82" s="27"/>
-      <c r="U82" s="27"/>
-      <c r="V82" s="27"/>
-      <c r="W82" s="27"/>
-      <c r="X82" s="27"/>
-      <c r="Y82" s="27"/>
-      <c r="Z82" s="27"/>
-    </row>
-    <row r="83" ht="12.0" customHeight="1">
-      <c r="A83" s="24"/>
-      <c r="B83" s="27"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="27"/>
-      <c r="E83" s="27"/>
-      <c r="F83" s="27"/>
-      <c r="G83" s="27"/>
-      <c r="H83" s="27"/>
-      <c r="I83" s="27"/>
-      <c r="J83" s="28"/>
-      <c r="K83" s="27"/>
-      <c r="L83" s="27"/>
-      <c r="M83" s="27"/>
-      <c r="N83" s="27"/>
-      <c r="O83" s="27"/>
-      <c r="P83" s="27"/>
-      <c r="Q83" s="27"/>
-      <c r="R83" s="27"/>
-      <c r="S83" s="27"/>
-      <c r="T83" s="27"/>
-      <c r="U83" s="27"/>
-      <c r="V83" s="27"/>
-      <c r="W83" s="27"/>
-      <c r="X83" s="27"/>
-      <c r="Y83" s="27"/>
-      <c r="Z83" s="27"/>
-    </row>
-    <row r="84" ht="12.0" customHeight="1">
-      <c r="A84" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B84" s="24"/>
-      <c r="C84" s="25"/>
-      <c r="D84" s="27"/>
-      <c r="E84" s="27"/>
-      <c r="F84" s="27"/>
-      <c r="G84" s="27"/>
-      <c r="H84" s="27"/>
-      <c r="I84" s="27"/>
-      <c r="J84" s="28"/>
-      <c r="K84" s="27"/>
-      <c r="L84" s="27"/>
-      <c r="M84" s="27"/>
-      <c r="N84" s="27"/>
-      <c r="O84" s="27"/>
-      <c r="P84" s="27"/>
-      <c r="Q84" s="27"/>
-      <c r="R84" s="27"/>
-      <c r="S84" s="27"/>
-      <c r="T84" s="27"/>
-      <c r="U84" s="27"/>
-      <c r="V84" s="27"/>
-      <c r="W84" s="27"/>
-      <c r="X84" s="27"/>
-      <c r="Y84" s="27"/>
-      <c r="Z84" s="27"/>
-    </row>
-    <row r="85" ht="12.0" customHeight="1">
-      <c r="A85" s="24"/>
-      <c r="B85" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C85" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D85" s="27"/>
-      <c r="E85" s="27"/>
-      <c r="F85" s="27"/>
-      <c r="G85" s="27"/>
-      <c r="H85" s="27"/>
-      <c r="I85" s="27"/>
-      <c r="J85" s="28"/>
-      <c r="K85" s="27"/>
-      <c r="L85" s="27"/>
-      <c r="M85" s="27"/>
-      <c r="N85" s="27"/>
-      <c r="O85" s="27"/>
-      <c r="P85" s="27"/>
-      <c r="Q85" s="27"/>
-      <c r="R85" s="27"/>
-      <c r="S85" s="27"/>
-      <c r="T85" s="27"/>
-      <c r="U85" s="27"/>
-      <c r="V85" s="27"/>
-      <c r="W85" s="27"/>
-      <c r="X85" s="27"/>
-      <c r="Y85" s="27"/>
-      <c r="Z85" s="27"/>
-    </row>
-    <row r="86" ht="12.0" customHeight="1">
-      <c r="A86" s="24"/>
-      <c r="B86" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C86" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D86" s="27"/>
-      <c r="E86" s="27"/>
-      <c r="F86" s="27"/>
-      <c r="G86" s="27"/>
-      <c r="H86" s="27"/>
-      <c r="I86" s="27"/>
-      <c r="J86" s="28"/>
-      <c r="K86" s="27"/>
-      <c r="L86" s="27"/>
-      <c r="M86" s="27"/>
-      <c r="N86" s="27"/>
-      <c r="O86" s="27"/>
-      <c r="P86" s="27"/>
-      <c r="Q86" s="27"/>
-      <c r="R86" s="27"/>
-      <c r="S86" s="27"/>
-      <c r="T86" s="27"/>
-      <c r="U86" s="27"/>
-      <c r="V86" s="27"/>
-      <c r="W86" s="27"/>
-      <c r="X86" s="27"/>
-      <c r="Y86" s="27"/>
-      <c r="Z86" s="27"/>
-    </row>
-    <row r="87" ht="12.0" customHeight="1">
-      <c r="A87" s="24"/>
-      <c r="B87" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C87" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D87" s="27"/>
-      <c r="E87" s="27"/>
-      <c r="F87" s="27"/>
-      <c r="G87" s="27"/>
-      <c r="H87" s="27"/>
-      <c r="I87" s="27"/>
-      <c r="J87" s="28"/>
-      <c r="K87" s="27"/>
-      <c r="L87" s="27"/>
-      <c r="M87" s="27"/>
-      <c r="N87" s="27"/>
-      <c r="O87" s="27"/>
-      <c r="P87" s="27"/>
-      <c r="Q87" s="27"/>
-      <c r="R87" s="27"/>
-      <c r="S87" s="27"/>
-      <c r="T87" s="27"/>
-      <c r="U87" s="27"/>
-      <c r="V87" s="27"/>
-      <c r="W87" s="27"/>
-      <c r="X87" s="27"/>
-      <c r="Y87" s="27"/>
-      <c r="Z87" s="27"/>
-    </row>
-    <row r="88" ht="12.0" customHeight="1">
-      <c r="A88" s="24"/>
-      <c r="B88" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C88" s="25"/>
-      <c r="D88" s="27"/>
-      <c r="E88" s="27"/>
-      <c r="F88" s="27"/>
-      <c r="G88" s="27"/>
-      <c r="H88" s="27"/>
-      <c r="I88" s="27"/>
-      <c r="J88" s="28"/>
-      <c r="K88" s="27"/>
-      <c r="L88" s="27"/>
-      <c r="M88" s="27"/>
-      <c r="N88" s="27"/>
-      <c r="O88" s="27"/>
-      <c r="P88" s="27"/>
-      <c r="Q88" s="27"/>
-      <c r="R88" s="27"/>
-      <c r="S88" s="27"/>
-      <c r="T88" s="27"/>
-      <c r="U88" s="27"/>
-      <c r="V88" s="27"/>
-      <c r="W88" s="27"/>
-      <c r="X88" s="27"/>
-      <c r="Y88" s="27"/>
-      <c r="Z88" s="27"/>
-    </row>
-    <row r="89" ht="12.0" customHeight="1">
-      <c r="A89" s="24"/>
-      <c r="B89" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C89" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="D89" s="27"/>
-      <c r="E89" s="27"/>
-      <c r="F89" s="27"/>
-      <c r="G89" s="27"/>
-      <c r="H89" s="27"/>
-      <c r="I89" s="27"/>
-      <c r="J89" s="28"/>
-      <c r="K89" s="27"/>
-      <c r="L89" s="27"/>
-      <c r="M89" s="27"/>
-      <c r="N89" s="27"/>
-      <c r="O89" s="27"/>
-      <c r="P89" s="27"/>
-      <c r="Q89" s="27"/>
-      <c r="R89" s="27"/>
-      <c r="S89" s="27"/>
-      <c r="T89" s="27"/>
-      <c r="U89" s="27"/>
-      <c r="V89" s="27"/>
-      <c r="W89" s="27"/>
-      <c r="X89" s="27"/>
-      <c r="Y89" s="27"/>
-      <c r="Z89" s="27"/>
-    </row>
-    <row r="90" ht="12.0" customHeight="1">
-      <c r="A90" s="24"/>
-      <c r="B90" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C90" s="31">
-        <v>-1.0E20</v>
-      </c>
-      <c r="D90" s="27"/>
-      <c r="E90" s="27"/>
-      <c r="F90" s="27"/>
-      <c r="G90" s="27"/>
-      <c r="H90" s="27"/>
-      <c r="I90" s="27"/>
-      <c r="J90" s="28"/>
-      <c r="K90" s="27"/>
-      <c r="L90" s="27"/>
-      <c r="M90" s="27"/>
-      <c r="N90" s="27"/>
-      <c r="O90" s="27"/>
-      <c r="P90" s="27"/>
-      <c r="Q90" s="27"/>
-      <c r="R90" s="27"/>
-      <c r="S90" s="27"/>
-      <c r="T90" s="27"/>
-      <c r="U90" s="27"/>
-      <c r="V90" s="27"/>
-      <c r="W90" s="27"/>
-      <c r="X90" s="27"/>
-      <c r="Y90" s="27"/>
-      <c r="Z90" s="27"/>
-    </row>
-    <row r="91" ht="12.0" customHeight="1">
-      <c r="A91" s="24"/>
-      <c r="B91" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C91" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="D91" s="27"/>
-      <c r="E91" s="27"/>
-      <c r="F91" s="27"/>
-      <c r="G91" s="27"/>
-      <c r="H91" s="27"/>
-      <c r="I91" s="27"/>
-      <c r="J91" s="28"/>
-      <c r="K91" s="27"/>
-      <c r="L91" s="27"/>
-      <c r="M91" s="27"/>
-      <c r="N91" s="27"/>
-      <c r="O91" s="27"/>
-      <c r="P91" s="27"/>
-      <c r="Q91" s="27"/>
-      <c r="R91" s="27"/>
-      <c r="S91" s="27"/>
-      <c r="T91" s="27"/>
-      <c r="U91" s="27"/>
-      <c r="V91" s="27"/>
-      <c r="W91" s="27"/>
-      <c r="X91" s="27"/>
-      <c r="Y91" s="27"/>
-      <c r="Z91" s="27"/>
-    </row>
-    <row r="92" ht="12.0" customHeight="1">
-      <c r="A92" s="24"/>
-      <c r="B92" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C92" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="D92" s="27"/>
-      <c r="E92" s="27"/>
-      <c r="F92" s="27"/>
-      <c r="G92" s="27"/>
-      <c r="H92" s="27"/>
-      <c r="I92" s="27"/>
-      <c r="J92" s="28"/>
-      <c r="K92" s="27"/>
-      <c r="L92" s="27"/>
-      <c r="M92" s="27"/>
-      <c r="N92" s="27"/>
-      <c r="O92" s="27"/>
-      <c r="P92" s="27"/>
-      <c r="Q92" s="27"/>
-      <c r="R92" s="27"/>
-      <c r="S92" s="27"/>
-      <c r="T92" s="27"/>
-      <c r="U92" s="27"/>
-      <c r="V92" s="27"/>
-      <c r="W92" s="27"/>
-      <c r="X92" s="27"/>
-      <c r="Y92" s="27"/>
-      <c r="Z92" s="27"/>
-    </row>
-    <row r="93" ht="12.0" customHeight="1">
-      <c r="A93" s="24"/>
-      <c r="B93" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C93" s="28"/>
-      <c r="D93" s="27"/>
-      <c r="E93" s="27"/>
-      <c r="F93" s="27"/>
-      <c r="G93" s="27"/>
-      <c r="H93" s="27"/>
-      <c r="I93" s="27"/>
-      <c r="J93" s="28"/>
-      <c r="K93" s="27"/>
-      <c r="L93" s="27"/>
-      <c r="M93" s="27"/>
-      <c r="N93" s="27"/>
-      <c r="O93" s="27"/>
-      <c r="P93" s="27"/>
-      <c r="Q93" s="27"/>
-      <c r="R93" s="27"/>
-      <c r="S93" s="27"/>
-      <c r="T93" s="27"/>
-      <c r="U93" s="27"/>
-      <c r="V93" s="27"/>
-      <c r="W93" s="27"/>
-      <c r="X93" s="27"/>
-      <c r="Y93" s="27"/>
-      <c r="Z93" s="27"/>
-    </row>
-    <row r="94" ht="12.0" customHeight="1">
-      <c r="A94" s="24"/>
-      <c r="B94" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C94" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D94" s="27"/>
-      <c r="E94" s="27"/>
-      <c r="F94" s="27"/>
-      <c r="G94" s="27"/>
-      <c r="H94" s="27"/>
-      <c r="I94" s="27"/>
-      <c r="J94" s="28"/>
-      <c r="K94" s="27"/>
-      <c r="L94" s="27"/>
-      <c r="M94" s="27"/>
-      <c r="N94" s="27"/>
-      <c r="O94" s="27"/>
-      <c r="P94" s="27"/>
-      <c r="Q94" s="27"/>
-      <c r="R94" s="27"/>
-      <c r="S94" s="27"/>
-      <c r="T94" s="27"/>
-      <c r="U94" s="27"/>
-      <c r="V94" s="27"/>
-      <c r="W94" s="27"/>
-      <c r="X94" s="27"/>
-      <c r="Y94" s="27"/>
-      <c r="Z94" s="27"/>
-    </row>
-    <row r="95" ht="12.0" customHeight="1">
-      <c r="A95" s="24"/>
-      <c r="B95" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C95" s="29"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="27"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="27"/>
-      <c r="H95" s="27"/>
-      <c r="I95" s="27"/>
-      <c r="J95" s="28"/>
-      <c r="K95" s="27"/>
-      <c r="L95" s="27"/>
-      <c r="M95" s="27"/>
-      <c r="N95" s="27"/>
-      <c r="O95" s="27"/>
-      <c r="P95" s="27"/>
-      <c r="Q95" s="27"/>
-      <c r="R95" s="27"/>
-      <c r="S95" s="27"/>
-      <c r="T95" s="27"/>
-      <c r="U95" s="27"/>
-      <c r="V95" s="27"/>
-      <c r="W95" s="27"/>
-      <c r="X95" s="27"/>
-      <c r="Y95" s="27"/>
-      <c r="Z95" s="27"/>
-    </row>
-    <row r="96" ht="12.0" customHeight="1">
-      <c r="A96" s="24"/>
-      <c r="B96" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C96" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="D96" s="27"/>
-      <c r="E96" s="27"/>
-      <c r="F96" s="27"/>
-      <c r="G96" s="27"/>
-      <c r="H96" s="27"/>
-      <c r="I96" s="27"/>
-      <c r="J96" s="28"/>
-      <c r="K96" s="27"/>
-      <c r="L96" s="27"/>
-      <c r="M96" s="27"/>
-      <c r="N96" s="27"/>
-      <c r="O96" s="27"/>
-      <c r="P96" s="27"/>
-      <c r="Q96" s="27"/>
-      <c r="R96" s="27"/>
-      <c r="S96" s="27"/>
-      <c r="T96" s="27"/>
-      <c r="U96" s="27"/>
-      <c r="V96" s="27"/>
-      <c r="W96" s="27"/>
-      <c r="X96" s="27"/>
-      <c r="Y96" s="27"/>
-      <c r="Z96" s="27"/>
-    </row>
-    <row r="97" ht="12.0" customHeight="1">
-      <c r="A97" s="24"/>
-      <c r="B97" s="27"/>
-      <c r="C97" s="29"/>
-      <c r="D97" s="27"/>
-      <c r="E97" s="27"/>
-      <c r="F97" s="27"/>
-      <c r="G97" s="27"/>
-      <c r="H97" s="27"/>
-      <c r="I97" s="27"/>
-      <c r="J97" s="28"/>
-      <c r="K97" s="27"/>
-      <c r="L97" s="27"/>
-      <c r="M97" s="27"/>
-      <c r="N97" s="27"/>
-      <c r="O97" s="27"/>
-      <c r="P97" s="27"/>
-      <c r="Q97" s="27"/>
-      <c r="R97" s="27"/>
-      <c r="S97" s="27"/>
-      <c r="T97" s="27"/>
-      <c r="U97" s="27"/>
-      <c r="V97" s="27"/>
-      <c r="W97" s="27"/>
-      <c r="X97" s="27"/>
-      <c r="Y97" s="27"/>
-      <c r="Z97" s="27"/>
-    </row>
-    <row r="98" ht="12.0" customHeight="1">
-      <c r="A98" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="B98" s="24"/>
-      <c r="C98" s="25"/>
-      <c r="D98" s="27"/>
-      <c r="E98" s="27"/>
-      <c r="F98" s="27"/>
-      <c r="G98" s="27"/>
-      <c r="H98" s="27"/>
-      <c r="I98" s="27"/>
-      <c r="J98" s="28"/>
-      <c r="K98" s="27"/>
-      <c r="L98" s="27"/>
-      <c r="M98" s="27"/>
-      <c r="N98" s="27"/>
-      <c r="O98" s="27"/>
-      <c r="P98" s="27"/>
-      <c r="Q98" s="27"/>
-      <c r="R98" s="27"/>
-      <c r="S98" s="27"/>
-      <c r="T98" s="27"/>
-      <c r="U98" s="27"/>
-      <c r="V98" s="27"/>
-      <c r="W98" s="27"/>
-      <c r="X98" s="27"/>
-      <c r="Y98" s="27"/>
-      <c r="Z98" s="27"/>
-    </row>
-    <row r="99" ht="12.0" customHeight="1">
-      <c r="A99" s="24"/>
-      <c r="B99" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C99" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D99" s="27"/>
-      <c r="E99" s="27"/>
-      <c r="F99" s="27"/>
-      <c r="G99" s="27"/>
-      <c r="H99" s="27"/>
-      <c r="I99" s="27"/>
-      <c r="J99" s="28"/>
-      <c r="K99" s="27"/>
-      <c r="L99" s="27"/>
-      <c r="M99" s="27"/>
-      <c r="N99" s="27"/>
-      <c r="O99" s="27"/>
-      <c r="P99" s="27"/>
-      <c r="Q99" s="27"/>
-      <c r="R99" s="27"/>
-      <c r="S99" s="27"/>
-      <c r="T99" s="27"/>
-      <c r="U99" s="27"/>
-      <c r="V99" s="27"/>
-      <c r="W99" s="27"/>
-      <c r="X99" s="27"/>
-      <c r="Y99" s="27"/>
-      <c r="Z99" s="27"/>
-    </row>
-    <row r="100" ht="12.0" customHeight="1">
-      <c r="A100" s="24"/>
-      <c r="B100" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C100" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D100" s="27"/>
-      <c r="E100" s="27"/>
-      <c r="F100" s="27"/>
-      <c r="G100" s="27"/>
-      <c r="H100" s="27"/>
-      <c r="I100" s="27"/>
-      <c r="J100" s="28"/>
-      <c r="K100" s="27"/>
-      <c r="L100" s="27"/>
-      <c r="M100" s="27"/>
-      <c r="N100" s="27"/>
-      <c r="O100" s="27"/>
-      <c r="P100" s="27"/>
-      <c r="Q100" s="27"/>
-      <c r="R100" s="27"/>
-      <c r="S100" s="27"/>
-      <c r="T100" s="27"/>
-      <c r="U100" s="27"/>
-      <c r="V100" s="27"/>
-      <c r="W100" s="27"/>
-      <c r="X100" s="27"/>
-      <c r="Y100" s="27"/>
-      <c r="Z100" s="27"/>
-    </row>
-    <row r="101" ht="12.0" customHeight="1">
-      <c r="A101" s="24"/>
-      <c r="B101" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C101" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D101" s="27"/>
-      <c r="E101" s="27"/>
-      <c r="F101" s="27"/>
-      <c r="G101" s="27"/>
-      <c r="H101" s="27"/>
-      <c r="I101" s="27"/>
-      <c r="J101" s="28"/>
-      <c r="K101" s="27"/>
-      <c r="L101" s="27"/>
-      <c r="M101" s="27"/>
-      <c r="N101" s="27"/>
-      <c r="O101" s="27"/>
-      <c r="P101" s="27"/>
-      <c r="Q101" s="27"/>
-      <c r="R101" s="27"/>
-      <c r="S101" s="27"/>
-      <c r="T101" s="27"/>
-      <c r="U101" s="27"/>
-      <c r="V101" s="27"/>
-      <c r="W101" s="27"/>
-      <c r="X101" s="27"/>
-      <c r="Y101" s="27"/>
-      <c r="Z101" s="27"/>
-    </row>
-    <row r="102" ht="12.0" customHeight="1">
-      <c r="A102" s="24"/>
-      <c r="B102" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C102" s="25"/>
-      <c r="D102" s="27"/>
-      <c r="E102" s="27"/>
-      <c r="F102" s="27"/>
-      <c r="G102" s="27"/>
-      <c r="H102" s="27"/>
-      <c r="I102" s="27"/>
-      <c r="J102" s="28"/>
-      <c r="K102" s="27"/>
-      <c r="L102" s="27"/>
-      <c r="M102" s="27"/>
-      <c r="N102" s="27"/>
-      <c r="O102" s="27"/>
-      <c r="P102" s="27"/>
-      <c r="Q102" s="27"/>
-      <c r="R102" s="27"/>
-      <c r="S102" s="27"/>
-      <c r="T102" s="27"/>
-      <c r="U102" s="27"/>
-      <c r="V102" s="27"/>
-      <c r="W102" s="27"/>
-      <c r="X102" s="27"/>
-      <c r="Y102" s="27"/>
-      <c r="Z102" s="27"/>
-    </row>
-    <row r="103" ht="12.0" customHeight="1">
-      <c r="A103" s="24"/>
-      <c r="B103" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C103" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="D103" s="27"/>
-      <c r="E103" s="27"/>
-      <c r="F103" s="27"/>
-      <c r="G103" s="27"/>
-      <c r="H103" s="27"/>
-      <c r="I103" s="27"/>
-      <c r="J103" s="28"/>
-      <c r="K103" s="27"/>
-      <c r="L103" s="27"/>
-      <c r="M103" s="27"/>
-      <c r="N103" s="27"/>
-      <c r="O103" s="27"/>
-      <c r="P103" s="27"/>
-      <c r="Q103" s="27"/>
-      <c r="R103" s="27"/>
-      <c r="S103" s="27"/>
-      <c r="T103" s="27"/>
-      <c r="U103" s="27"/>
-      <c r="V103" s="27"/>
-      <c r="W103" s="27"/>
-      <c r="X103" s="27"/>
-      <c r="Y103" s="27"/>
-      <c r="Z103" s="27"/>
-    </row>
-    <row r="104" ht="12.0" customHeight="1">
-      <c r="A104" s="24"/>
-      <c r="B104" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C104" s="31">
-        <v>-1.0E20</v>
-      </c>
-      <c r="D104" s="27"/>
-      <c r="E104" s="27"/>
-      <c r="F104" s="27"/>
-      <c r="G104" s="27"/>
-      <c r="H104" s="27"/>
-      <c r="I104" s="27"/>
-      <c r="J104" s="28"/>
-      <c r="K104" s="27"/>
-      <c r="L104" s="27"/>
-      <c r="M104" s="27"/>
-      <c r="N104" s="27"/>
-      <c r="O104" s="27"/>
-      <c r="P104" s="27"/>
-      <c r="Q104" s="27"/>
-      <c r="R104" s="27"/>
-      <c r="S104" s="27"/>
-      <c r="T104" s="27"/>
-      <c r="U104" s="27"/>
-      <c r="V104" s="27"/>
-      <c r="W104" s="27"/>
-      <c r="X104" s="27"/>
-      <c r="Y104" s="27"/>
-      <c r="Z104" s="27"/>
-    </row>
-    <row r="105" ht="12.0" customHeight="1">
-      <c r="A105" s="24"/>
-      <c r="B105" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C105" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="D105" s="27"/>
-      <c r="E105" s="27"/>
-      <c r="F105" s="27"/>
-      <c r="G105" s="27"/>
-      <c r="H105" s="27"/>
-      <c r="I105" s="27"/>
-      <c r="J105" s="28"/>
-      <c r="K105" s="27"/>
-      <c r="L105" s="27"/>
-      <c r="M105" s="27"/>
-      <c r="N105" s="27"/>
-      <c r="O105" s="27"/>
-      <c r="P105" s="27"/>
-      <c r="Q105" s="27"/>
-      <c r="R105" s="27"/>
-      <c r="S105" s="27"/>
-      <c r="T105" s="27"/>
-      <c r="U105" s="27"/>
-      <c r="V105" s="27"/>
-      <c r="W105" s="27"/>
-      <c r="X105" s="27"/>
-      <c r="Y105" s="27"/>
-      <c r="Z105" s="27"/>
-    </row>
-    <row r="106" ht="12.0" customHeight="1">
-      <c r="A106" s="24"/>
-      <c r="B106" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C106" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="D106" s="27"/>
-      <c r="E106" s="27"/>
-      <c r="F106" s="27"/>
-      <c r="G106" s="27"/>
-      <c r="H106" s="27"/>
-      <c r="I106" s="27"/>
-      <c r="J106" s="28"/>
-      <c r="K106" s="27"/>
-      <c r="L106" s="27"/>
-      <c r="M106" s="27"/>
-      <c r="N106" s="27"/>
-      <c r="O106" s="27"/>
-      <c r="P106" s="27"/>
-      <c r="Q106" s="27"/>
-      <c r="R106" s="27"/>
-      <c r="S106" s="27"/>
-      <c r="T106" s="27"/>
-      <c r="U106" s="27"/>
-      <c r="V106" s="27"/>
-      <c r="W106" s="27"/>
-      <c r="X106" s="27"/>
-      <c r="Y106" s="27"/>
-      <c r="Z106" s="27"/>
-    </row>
-    <row r="107" ht="12.0" customHeight="1">
-      <c r="A107" s="24"/>
-      <c r="B107" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C107" s="28"/>
-      <c r="D107" s="27"/>
-      <c r="E107" s="27"/>
-      <c r="F107" s="27"/>
-      <c r="G107" s="27"/>
-      <c r="H107" s="27"/>
-      <c r="I107" s="27"/>
-      <c r="J107" s="28"/>
-      <c r="K107" s="27"/>
-      <c r="L107" s="27"/>
-      <c r="M107" s="27"/>
-      <c r="N107" s="27"/>
-      <c r="O107" s="27"/>
-      <c r="P107" s="27"/>
-      <c r="Q107" s="27"/>
-      <c r="R107" s="27"/>
-      <c r="S107" s="27"/>
-      <c r="T107" s="27"/>
-      <c r="U107" s="27"/>
-      <c r="V107" s="27"/>
-      <c r="W107" s="27"/>
-      <c r="X107" s="27"/>
-      <c r="Y107" s="27"/>
-      <c r="Z107" s="27"/>
-    </row>
-    <row r="108" ht="12.0" customHeight="1">
-      <c r="A108" s="24"/>
-      <c r="B108" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C108" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D108" s="27"/>
-      <c r="E108" s="27"/>
-      <c r="F108" s="27"/>
-      <c r="G108" s="27"/>
-      <c r="H108" s="27"/>
-      <c r="I108" s="27"/>
-      <c r="J108" s="28"/>
-      <c r="K108" s="27"/>
-      <c r="L108" s="27"/>
-      <c r="M108" s="27"/>
-      <c r="N108" s="27"/>
-      <c r="O108" s="27"/>
-      <c r="P108" s="27"/>
-      <c r="Q108" s="27"/>
-      <c r="R108" s="27"/>
-      <c r="S108" s="27"/>
-      <c r="T108" s="27"/>
-      <c r="U108" s="27"/>
-      <c r="V108" s="27"/>
-      <c r="W108" s="27"/>
-      <c r="X108" s="27"/>
-      <c r="Y108" s="27"/>
-      <c r="Z108" s="27"/>
-    </row>
-    <row r="109" ht="12.0" customHeight="1">
-      <c r="A109" s="24"/>
-      <c r="B109" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C109" s="29"/>
-      <c r="D109" s="27"/>
-      <c r="E109" s="27"/>
-      <c r="F109" s="27"/>
-      <c r="G109" s="27"/>
-      <c r="H109" s="27"/>
-      <c r="I109" s="27"/>
-      <c r="J109" s="28"/>
-      <c r="K109" s="27"/>
-      <c r="L109" s="27"/>
-      <c r="M109" s="27"/>
-      <c r="N109" s="27"/>
-      <c r="O109" s="27"/>
-      <c r="P109" s="27"/>
-      <c r="Q109" s="27"/>
-      <c r="R109" s="27"/>
-      <c r="S109" s="27"/>
-      <c r="T109" s="27"/>
-      <c r="U109" s="27"/>
-      <c r="V109" s="27"/>
-      <c r="W109" s="27"/>
-      <c r="X109" s="27"/>
-      <c r="Y109" s="27"/>
-      <c r="Z109" s="27"/>
+      <c r="C109" s="27"/>
+      <c r="D109" s="22"/>
+      <c r="E109" s="22"/>
+      <c r="F109" s="22"/>
+      <c r="G109" s="22"/>
+      <c r="H109" s="22"/>
+      <c r="I109" s="22"/>
+      <c r="J109" s="26"/>
+      <c r="K109" s="22"/>
+      <c r="L109" s="22"/>
+      <c r="M109" s="22"/>
+      <c r="N109" s="22"/>
+      <c r="O109" s="22"/>
+      <c r="P109" s="22"/>
+      <c r="Q109" s="22"/>
+      <c r="R109" s="22"/>
+      <c r="S109" s="22"/>
+      <c r="T109" s="22"/>
+      <c r="U109" s="22"/>
+      <c r="V109" s="22"/>
+      <c r="W109" s="22"/>
+      <c r="X109" s="22"/>
+      <c r="Y109" s="22"/>
+      <c r="Z109" s="22"/>
     </row>
     <row r="110" ht="12.0" customHeight="1">
       <c r="A110" s="10"/>
-      <c r="B110" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C110" s="29" t="s">
+      <c r="B110" s="22" t="s">
         <v>53</v>
+      </c>
+      <c r="C110" s="27" t="s">
+        <v>54</v>
       </c>
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
@@ -12638,7 +12633,7 @@
     <row r="111" ht="12.0" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="10"/>
-      <c r="C111" s="18"/>
+      <c r="C111" s="17"/>
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
@@ -12664,883 +12659,883 @@
       <c r="Z111" s="10"/>
     </row>
     <row r="112" ht="12.0" customHeight="1">
-      <c r="A112" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="B112" s="24"/>
-      <c r="C112" s="25"/>
-      <c r="D112" s="27"/>
-      <c r="E112" s="27"/>
-      <c r="F112" s="27"/>
-      <c r="G112" s="27"/>
-      <c r="H112" s="27"/>
-      <c r="I112" s="27"/>
-      <c r="J112" s="28"/>
-      <c r="K112" s="27"/>
-      <c r="L112" s="27"/>
-      <c r="M112" s="27"/>
-      <c r="N112" s="27"/>
-      <c r="O112" s="27"/>
-      <c r="P112" s="27"/>
-      <c r="Q112" s="27"/>
-      <c r="R112" s="27"/>
-      <c r="S112" s="27"/>
-      <c r="T112" s="27"/>
-      <c r="U112" s="27"/>
-      <c r="V112" s="27"/>
-      <c r="W112" s="27"/>
-      <c r="X112" s="27"/>
-      <c r="Y112" s="27"/>
-      <c r="Z112" s="27"/>
+      <c r="A112" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B112" s="23"/>
+      <c r="C112" s="24"/>
+      <c r="D112" s="22"/>
+      <c r="E112" s="22"/>
+      <c r="F112" s="22"/>
+      <c r="G112" s="22"/>
+      <c r="H112" s="22"/>
+      <c r="I112" s="22"/>
+      <c r="J112" s="26"/>
+      <c r="K112" s="22"/>
+      <c r="L112" s="22"/>
+      <c r="M112" s="22"/>
+      <c r="N112" s="22"/>
+      <c r="O112" s="22"/>
+      <c r="P112" s="22"/>
+      <c r="Q112" s="22"/>
+      <c r="R112" s="22"/>
+      <c r="S112" s="22"/>
+      <c r="T112" s="22"/>
+      <c r="U112" s="22"/>
+      <c r="V112" s="22"/>
+      <c r="W112" s="22"/>
+      <c r="X112" s="22"/>
+      <c r="Y112" s="22"/>
+      <c r="Z112" s="22"/>
     </row>
     <row r="113" ht="12.0" customHeight="1">
-      <c r="A113" s="24"/>
-      <c r="B113" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C113" s="28" t="s">
+      <c r="A113" s="23"/>
+      <c r="B113" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D113" s="27"/>
-      <c r="E113" s="27"/>
-      <c r="F113" s="27"/>
-      <c r="G113" s="27"/>
-      <c r="H113" s="27"/>
-      <c r="I113" s="27"/>
-      <c r="J113" s="28"/>
-      <c r="K113" s="27"/>
-      <c r="L113" s="27"/>
-      <c r="M113" s="27"/>
-      <c r="N113" s="27"/>
-      <c r="O113" s="27"/>
-      <c r="P113" s="27"/>
-      <c r="Q113" s="27"/>
-      <c r="R113" s="27"/>
-      <c r="S113" s="27"/>
-      <c r="T113" s="27"/>
-      <c r="U113" s="27"/>
-      <c r="V113" s="27"/>
-      <c r="W113" s="27"/>
-      <c r="X113" s="27"/>
-      <c r="Y113" s="27"/>
-      <c r="Z113" s="27"/>
+      <c r="C113" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D113" s="22"/>
+      <c r="E113" s="22"/>
+      <c r="F113" s="22"/>
+      <c r="G113" s="22"/>
+      <c r="H113" s="22"/>
+      <c r="I113" s="22"/>
+      <c r="J113" s="26"/>
+      <c r="K113" s="22"/>
+      <c r="L113" s="22"/>
+      <c r="M113" s="22"/>
+      <c r="N113" s="22"/>
+      <c r="O113" s="22"/>
+      <c r="P113" s="22"/>
+      <c r="Q113" s="22"/>
+      <c r="R113" s="22"/>
+      <c r="S113" s="22"/>
+      <c r="T113" s="22"/>
+      <c r="U113" s="22"/>
+      <c r="V113" s="22"/>
+      <c r="W113" s="22"/>
+      <c r="X113" s="22"/>
+      <c r="Y113" s="22"/>
+      <c r="Z113" s="22"/>
     </row>
     <row r="114" ht="12.0" customHeight="1">
-      <c r="A114" s="24"/>
-      <c r="B114" s="27" t="s">
+      <c r="A114" s="23"/>
+      <c r="B114" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D114" s="22"/>
+      <c r="E114" s="22"/>
+      <c r="F114" s="22"/>
+      <c r="G114" s="22"/>
+      <c r="H114" s="22"/>
+      <c r="I114" s="22"/>
+      <c r="J114" s="26"/>
+      <c r="K114" s="22"/>
+      <c r="L114" s="22"/>
+      <c r="M114" s="22"/>
+      <c r="N114" s="22"/>
+      <c r="O114" s="22"/>
+      <c r="P114" s="22"/>
+      <c r="Q114" s="22"/>
+      <c r="R114" s="22"/>
+      <c r="S114" s="22"/>
+      <c r="T114" s="22"/>
+      <c r="U114" s="22"/>
+      <c r="V114" s="22"/>
+      <c r="W114" s="22"/>
+      <c r="X114" s="22"/>
+      <c r="Y114" s="22"/>
+      <c r="Z114" s="22"/>
+    </row>
+    <row r="115" ht="12.0" customHeight="1">
+      <c r="A115" s="23"/>
+      <c r="B115" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C115" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D115" s="22"/>
+      <c r="E115" s="22"/>
+      <c r="F115" s="22"/>
+      <c r="G115" s="22"/>
+      <c r="H115" s="22"/>
+      <c r="I115" s="22"/>
+      <c r="J115" s="26"/>
+      <c r="K115" s="22"/>
+      <c r="L115" s="22"/>
+      <c r="M115" s="22"/>
+      <c r="N115" s="22"/>
+      <c r="O115" s="22"/>
+      <c r="P115" s="22"/>
+      <c r="Q115" s="22"/>
+      <c r="R115" s="22"/>
+      <c r="S115" s="22"/>
+      <c r="T115" s="22"/>
+      <c r="U115" s="22"/>
+      <c r="V115" s="22"/>
+      <c r="W115" s="22"/>
+      <c r="X115" s="22"/>
+      <c r="Y115" s="22"/>
+      <c r="Z115" s="22"/>
+    </row>
+    <row r="116" ht="12.0" customHeight="1">
+      <c r="A116" s="23"/>
+      <c r="B116" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C116" s="24"/>
+      <c r="D116" s="22"/>
+      <c r="E116" s="22"/>
+      <c r="F116" s="22"/>
+      <c r="G116" s="22"/>
+      <c r="H116" s="22"/>
+      <c r="I116" s="22"/>
+      <c r="J116" s="26"/>
+      <c r="K116" s="22"/>
+      <c r="L116" s="22"/>
+      <c r="M116" s="22"/>
+      <c r="N116" s="22"/>
+      <c r="O116" s="22"/>
+      <c r="P116" s="22"/>
+      <c r="Q116" s="22"/>
+      <c r="R116" s="22"/>
+      <c r="S116" s="22"/>
+      <c r="T116" s="22"/>
+      <c r="U116" s="22"/>
+      <c r="V116" s="22"/>
+      <c r="W116" s="22"/>
+      <c r="X116" s="22"/>
+      <c r="Y116" s="22"/>
+      <c r="Z116" s="22"/>
+    </row>
+    <row r="117" ht="12.0" customHeight="1">
+      <c r="A117" s="23"/>
+      <c r="B117" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C117" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D117" s="22"/>
+      <c r="E117" s="22"/>
+      <c r="F117" s="22"/>
+      <c r="G117" s="22"/>
+      <c r="H117" s="22"/>
+      <c r="I117" s="22"/>
+      <c r="J117" s="26"/>
+      <c r="K117" s="22"/>
+      <c r="L117" s="22"/>
+      <c r="M117" s="22"/>
+      <c r="N117" s="22"/>
+      <c r="O117" s="22"/>
+      <c r="P117" s="22"/>
+      <c r="Q117" s="22"/>
+      <c r="R117" s="22"/>
+      <c r="S117" s="22"/>
+      <c r="T117" s="22"/>
+      <c r="U117" s="22"/>
+      <c r="V117" s="22"/>
+      <c r="W117" s="22"/>
+      <c r="X117" s="22"/>
+      <c r="Y117" s="22"/>
+      <c r="Z117" s="22"/>
+    </row>
+    <row r="118" ht="12.0" customHeight="1">
+      <c r="A118" s="23"/>
+      <c r="B118" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C118" s="28">
+        <v>-1.0E20</v>
+      </c>
+      <c r="D118" s="22"/>
+      <c r="E118" s="22"/>
+      <c r="F118" s="22"/>
+      <c r="G118" s="22"/>
+      <c r="H118" s="22"/>
+      <c r="I118" s="22"/>
+      <c r="J118" s="26"/>
+      <c r="K118" s="22"/>
+      <c r="L118" s="22"/>
+      <c r="M118" s="22"/>
+      <c r="N118" s="22"/>
+      <c r="O118" s="22"/>
+      <c r="P118" s="22"/>
+      <c r="Q118" s="22"/>
+      <c r="R118" s="22"/>
+      <c r="S118" s="22"/>
+      <c r="T118" s="22"/>
+      <c r="U118" s="22"/>
+      <c r="V118" s="22"/>
+      <c r="W118" s="22"/>
+      <c r="X118" s="22"/>
+      <c r="Y118" s="22"/>
+      <c r="Z118" s="22"/>
+    </row>
+    <row r="119" ht="12.0" customHeight="1">
+      <c r="A119" s="23"/>
+      <c r="B119" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C119" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D119" s="22"/>
+      <c r="E119" s="22"/>
+      <c r="F119" s="22"/>
+      <c r="G119" s="22"/>
+      <c r="H119" s="22"/>
+      <c r="I119" s="22"/>
+      <c r="J119" s="26"/>
+      <c r="K119" s="22"/>
+      <c r="L119" s="22"/>
+      <c r="M119" s="22"/>
+      <c r="N119" s="22"/>
+      <c r="O119" s="22"/>
+      <c r="P119" s="22"/>
+      <c r="Q119" s="22"/>
+      <c r="R119" s="22"/>
+      <c r="S119" s="22"/>
+      <c r="T119" s="22"/>
+      <c r="U119" s="22"/>
+      <c r="V119" s="22"/>
+      <c r="W119" s="22"/>
+      <c r="X119" s="22"/>
+      <c r="Y119" s="22"/>
+      <c r="Z119" s="22"/>
+    </row>
+    <row r="120" ht="12.0" customHeight="1">
+      <c r="A120" s="23"/>
+      <c r="B120" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C120" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D120" s="22"/>
+      <c r="E120" s="22"/>
+      <c r="F120" s="22"/>
+      <c r="G120" s="22"/>
+      <c r="H120" s="22"/>
+      <c r="I120" s="22"/>
+      <c r="J120" s="26"/>
+      <c r="K120" s="22"/>
+      <c r="L120" s="22"/>
+      <c r="M120" s="22"/>
+      <c r="N120" s="22"/>
+      <c r="O120" s="22"/>
+      <c r="P120" s="22"/>
+      <c r="Q120" s="22"/>
+      <c r="R120" s="22"/>
+      <c r="S120" s="22"/>
+      <c r="T120" s="22"/>
+      <c r="U120" s="22"/>
+      <c r="V120" s="22"/>
+      <c r="W120" s="22"/>
+      <c r="X120" s="22"/>
+      <c r="Y120" s="22"/>
+      <c r="Z120" s="22"/>
+    </row>
+    <row r="121" ht="12.0" customHeight="1">
+      <c r="A121" s="23"/>
+      <c r="B121" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C121" s="26"/>
+      <c r="D121" s="22"/>
+      <c r="E121" s="22"/>
+      <c r="F121" s="22"/>
+      <c r="G121" s="22"/>
+      <c r="H121" s="22"/>
+      <c r="I121" s="22"/>
+      <c r="J121" s="26"/>
+      <c r="K121" s="22"/>
+      <c r="L121" s="22"/>
+      <c r="M121" s="22"/>
+      <c r="N121" s="22"/>
+      <c r="O121" s="22"/>
+      <c r="P121" s="22"/>
+      <c r="Q121" s="22"/>
+      <c r="R121" s="22"/>
+      <c r="S121" s="22"/>
+      <c r="T121" s="22"/>
+      <c r="U121" s="22"/>
+      <c r="V121" s="22"/>
+      <c r="W121" s="22"/>
+      <c r="X121" s="22"/>
+      <c r="Y121" s="22"/>
+      <c r="Z121" s="22"/>
+    </row>
+    <row r="122" ht="12.0" customHeight="1">
+      <c r="A122" s="23"/>
+      <c r="B122" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C122" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D122" s="22"/>
+      <c r="E122" s="22"/>
+      <c r="F122" s="22"/>
+      <c r="G122" s="22"/>
+      <c r="H122" s="22"/>
+      <c r="I122" s="22"/>
+      <c r="J122" s="26"/>
+      <c r="K122" s="22"/>
+      <c r="L122" s="22"/>
+      <c r="M122" s="22"/>
+      <c r="N122" s="22"/>
+      <c r="O122" s="22"/>
+      <c r="P122" s="22"/>
+      <c r="Q122" s="22"/>
+      <c r="R122" s="22"/>
+      <c r="S122" s="22"/>
+      <c r="T122" s="22"/>
+      <c r="U122" s="22"/>
+      <c r="V122" s="22"/>
+      <c r="W122" s="22"/>
+      <c r="X122" s="22"/>
+      <c r="Y122" s="22"/>
+      <c r="Z122" s="22"/>
+    </row>
+    <row r="123" ht="12.0" customHeight="1">
+      <c r="A123" s="23"/>
+      <c r="B123" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C123" s="27"/>
+      <c r="D123" s="22"/>
+      <c r="E123" s="22"/>
+      <c r="F123" s="22"/>
+      <c r="G123" s="22"/>
+      <c r="H123" s="22"/>
+      <c r="I123" s="22"/>
+      <c r="J123" s="26"/>
+      <c r="K123" s="22"/>
+      <c r="L123" s="22"/>
+      <c r="M123" s="22"/>
+      <c r="N123" s="22"/>
+      <c r="O123" s="22"/>
+      <c r="P123" s="22"/>
+      <c r="Q123" s="22"/>
+      <c r="R123" s="22"/>
+      <c r="S123" s="22"/>
+      <c r="T123" s="22"/>
+      <c r="U123" s="22"/>
+      <c r="V123" s="22"/>
+      <c r="W123" s="22"/>
+      <c r="X123" s="22"/>
+      <c r="Y123" s="22"/>
+      <c r="Z123" s="22"/>
+    </row>
+    <row r="124" ht="12.0" customHeight="1">
+      <c r="A124" s="23"/>
+      <c r="B124" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C124" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D124" s="22"/>
+      <c r="E124" s="22"/>
+      <c r="F124" s="22"/>
+      <c r="G124" s="22"/>
+      <c r="H124" s="22"/>
+      <c r="I124" s="22"/>
+      <c r="J124" s="26"/>
+      <c r="K124" s="22"/>
+      <c r="L124" s="22"/>
+      <c r="M124" s="22"/>
+      <c r="N124" s="22"/>
+      <c r="O124" s="22"/>
+      <c r="P124" s="22"/>
+      <c r="Q124" s="22"/>
+      <c r="R124" s="22"/>
+      <c r="S124" s="22"/>
+      <c r="T124" s="22"/>
+      <c r="U124" s="22"/>
+      <c r="V124" s="22"/>
+      <c r="W124" s="22"/>
+      <c r="X124" s="22"/>
+      <c r="Y124" s="22"/>
+      <c r="Z124" s="22"/>
+    </row>
+    <row r="125" ht="12.0" customHeight="1">
+      <c r="A125" s="23"/>
+      <c r="B125" s="22"/>
+      <c r="C125" s="27"/>
+      <c r="D125" s="22"/>
+      <c r="E125" s="22"/>
+      <c r="F125" s="22"/>
+      <c r="G125" s="22"/>
+      <c r="H125" s="22"/>
+      <c r="I125" s="22"/>
+      <c r="J125" s="26"/>
+      <c r="K125" s="22"/>
+      <c r="L125" s="22"/>
+      <c r="M125" s="22"/>
+      <c r="N125" s="22"/>
+      <c r="O125" s="22"/>
+      <c r="P125" s="22"/>
+      <c r="Q125" s="22"/>
+      <c r="R125" s="22"/>
+      <c r="S125" s="22"/>
+      <c r="T125" s="22"/>
+      <c r="U125" s="22"/>
+      <c r="V125" s="22"/>
+      <c r="W125" s="22"/>
+      <c r="X125" s="22"/>
+      <c r="Y125" s="22"/>
+      <c r="Z125" s="22"/>
+    </row>
+    <row r="126" ht="12.0" customHeight="1">
+      <c r="A126" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B126" s="23"/>
+      <c r="C126" s="24"/>
+      <c r="D126" s="22"/>
+      <c r="E126" s="22"/>
+      <c r="F126" s="22"/>
+      <c r="G126" s="22"/>
+      <c r="H126" s="22"/>
+      <c r="I126" s="22"/>
+      <c r="J126" s="26"/>
+      <c r="K126" s="22"/>
+      <c r="L126" s="22"/>
+      <c r="M126" s="22"/>
+      <c r="N126" s="22"/>
+      <c r="O126" s="22"/>
+      <c r="P126" s="22"/>
+      <c r="Q126" s="22"/>
+      <c r="R126" s="22"/>
+      <c r="S126" s="22"/>
+      <c r="T126" s="22"/>
+      <c r="U126" s="22"/>
+      <c r="V126" s="22"/>
+      <c r="W126" s="22"/>
+      <c r="X126" s="22"/>
+      <c r="Y126" s="22"/>
+      <c r="Z126" s="22"/>
+    </row>
+    <row r="127" ht="12.0" customHeight="1">
+      <c r="A127" s="23"/>
+      <c r="B127" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C127" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C114" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D114" s="27"/>
-      <c r="E114" s="27"/>
-      <c r="F114" s="27"/>
-      <c r="G114" s="27"/>
-      <c r="H114" s="27"/>
-      <c r="I114" s="27"/>
-      <c r="J114" s="28"/>
-      <c r="K114" s="27"/>
-      <c r="L114" s="27"/>
-      <c r="M114" s="27"/>
-      <c r="N114" s="27"/>
-      <c r="O114" s="27"/>
-      <c r="P114" s="27"/>
-      <c r="Q114" s="27"/>
-      <c r="R114" s="27"/>
-      <c r="S114" s="27"/>
-      <c r="T114" s="27"/>
-      <c r="U114" s="27"/>
-      <c r="V114" s="27"/>
-      <c r="W114" s="27"/>
-      <c r="X114" s="27"/>
-      <c r="Y114" s="27"/>
-      <c r="Z114" s="27"/>
-    </row>
-    <row r="115" ht="12.0" customHeight="1">
-      <c r="A115" s="24"/>
-      <c r="B115" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C115" s="28" t="s">
+      <c r="D127" s="22"/>
+      <c r="E127" s="22"/>
+      <c r="F127" s="22"/>
+      <c r="G127" s="22"/>
+      <c r="H127" s="22"/>
+      <c r="I127" s="22"/>
+      <c r="J127" s="26"/>
+      <c r="K127" s="22"/>
+      <c r="L127" s="22"/>
+      <c r="M127" s="22"/>
+      <c r="N127" s="22"/>
+      <c r="O127" s="22"/>
+      <c r="P127" s="22"/>
+      <c r="Q127" s="22"/>
+      <c r="R127" s="22"/>
+      <c r="S127" s="22"/>
+      <c r="T127" s="22"/>
+      <c r="U127" s="22"/>
+      <c r="V127" s="22"/>
+      <c r="W127" s="22"/>
+      <c r="X127" s="22"/>
+      <c r="Y127" s="22"/>
+      <c r="Z127" s="22"/>
+    </row>
+    <row r="128" ht="12.0" customHeight="1">
+      <c r="A128" s="23"/>
+      <c r="B128" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C128" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="D115" s="27"/>
-      <c r="E115" s="27"/>
-      <c r="F115" s="27"/>
-      <c r="G115" s="27"/>
-      <c r="H115" s="27"/>
-      <c r="I115" s="27"/>
-      <c r="J115" s="28"/>
-      <c r="K115" s="27"/>
-      <c r="L115" s="27"/>
-      <c r="M115" s="27"/>
-      <c r="N115" s="27"/>
-      <c r="O115" s="27"/>
-      <c r="P115" s="27"/>
-      <c r="Q115" s="27"/>
-      <c r="R115" s="27"/>
-      <c r="S115" s="27"/>
-      <c r="T115" s="27"/>
-      <c r="U115" s="27"/>
-      <c r="V115" s="27"/>
-      <c r="W115" s="27"/>
-      <c r="X115" s="27"/>
-      <c r="Y115" s="27"/>
-      <c r="Z115" s="27"/>
-    </row>
-    <row r="116" ht="12.0" customHeight="1">
-      <c r="A116" s="24"/>
-      <c r="B116" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C116" s="25"/>
-      <c r="D116" s="27"/>
-      <c r="E116" s="27"/>
-      <c r="F116" s="27"/>
-      <c r="G116" s="27"/>
-      <c r="H116" s="27"/>
-      <c r="I116" s="27"/>
-      <c r="J116" s="28"/>
-      <c r="K116" s="27"/>
-      <c r="L116" s="27"/>
-      <c r="M116" s="27"/>
-      <c r="N116" s="27"/>
-      <c r="O116" s="27"/>
-      <c r="P116" s="27"/>
-      <c r="Q116" s="27"/>
-      <c r="R116" s="27"/>
-      <c r="S116" s="27"/>
-      <c r="T116" s="27"/>
-      <c r="U116" s="27"/>
-      <c r="V116" s="27"/>
-      <c r="W116" s="27"/>
-      <c r="X116" s="27"/>
-      <c r="Y116" s="27"/>
-      <c r="Z116" s="27"/>
-    </row>
-    <row r="117" ht="12.0" customHeight="1">
-      <c r="A117" s="24"/>
-      <c r="B117" s="27" t="s">
+      <c r="D128" s="22"/>
+      <c r="E128" s="22"/>
+      <c r="F128" s="22"/>
+      <c r="G128" s="22"/>
+      <c r="H128" s="22"/>
+      <c r="I128" s="22"/>
+      <c r="J128" s="26"/>
+      <c r="K128" s="22"/>
+      <c r="L128" s="22"/>
+      <c r="M128" s="22"/>
+      <c r="N128" s="22"/>
+      <c r="O128" s="22"/>
+      <c r="P128" s="22"/>
+      <c r="Q128" s="22"/>
+      <c r="R128" s="22"/>
+      <c r="S128" s="22"/>
+      <c r="T128" s="22"/>
+      <c r="U128" s="22"/>
+      <c r="V128" s="22"/>
+      <c r="W128" s="22"/>
+      <c r="X128" s="22"/>
+      <c r="Y128" s="22"/>
+      <c r="Z128" s="22"/>
+    </row>
+    <row r="129" ht="12.0" customHeight="1">
+      <c r="A129" s="23"/>
+      <c r="B129" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C129" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D129" s="22"/>
+      <c r="E129" s="22"/>
+      <c r="F129" s="22"/>
+      <c r="G129" s="22"/>
+      <c r="H129" s="22"/>
+      <c r="I129" s="22"/>
+      <c r="J129" s="26"/>
+      <c r="K129" s="22"/>
+      <c r="L129" s="22"/>
+      <c r="M129" s="22"/>
+      <c r="N129" s="22"/>
+      <c r="O129" s="22"/>
+      <c r="P129" s="22"/>
+      <c r="Q129" s="22"/>
+      <c r="R129" s="22"/>
+      <c r="S129" s="22"/>
+      <c r="T129" s="22"/>
+      <c r="U129" s="22"/>
+      <c r="V129" s="22"/>
+      <c r="W129" s="22"/>
+      <c r="X129" s="22"/>
+      <c r="Y129" s="22"/>
+      <c r="Z129" s="22"/>
+    </row>
+    <row r="130" ht="12.0" customHeight="1">
+      <c r="A130" s="23"/>
+      <c r="B130" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C117" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="D117" s="27"/>
-      <c r="E117" s="27"/>
-      <c r="F117" s="27"/>
-      <c r="G117" s="27"/>
-      <c r="H117" s="27"/>
-      <c r="I117" s="27"/>
-      <c r="J117" s="28"/>
-      <c r="K117" s="27"/>
-      <c r="L117" s="27"/>
-      <c r="M117" s="27"/>
-      <c r="N117" s="27"/>
-      <c r="O117" s="27"/>
-      <c r="P117" s="27"/>
-      <c r="Q117" s="27"/>
-      <c r="R117" s="27"/>
-      <c r="S117" s="27"/>
-      <c r="T117" s="27"/>
-      <c r="U117" s="27"/>
-      <c r="V117" s="27"/>
-      <c r="W117" s="27"/>
-      <c r="X117" s="27"/>
-      <c r="Y117" s="27"/>
-      <c r="Z117" s="27"/>
-    </row>
-    <row r="118" ht="12.0" customHeight="1">
-      <c r="A118" s="24"/>
-      <c r="B118" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C118" s="31">
+      <c r="C130" s="24"/>
+      <c r="D130" s="22"/>
+      <c r="E130" s="22"/>
+      <c r="F130" s="22"/>
+      <c r="G130" s="22"/>
+      <c r="H130" s="22"/>
+      <c r="I130" s="22"/>
+      <c r="J130" s="26"/>
+      <c r="K130" s="22"/>
+      <c r="L130" s="22"/>
+      <c r="M130" s="22"/>
+      <c r="N130" s="22"/>
+      <c r="O130" s="22"/>
+      <c r="P130" s="22"/>
+      <c r="Q130" s="22"/>
+      <c r="R130" s="22"/>
+      <c r="S130" s="22"/>
+      <c r="T130" s="22"/>
+      <c r="U130" s="22"/>
+      <c r="V130" s="22"/>
+      <c r="W130" s="22"/>
+      <c r="X130" s="22"/>
+      <c r="Y130" s="22"/>
+      <c r="Z130" s="22"/>
+    </row>
+    <row r="131" ht="12.0" customHeight="1">
+      <c r="A131" s="23"/>
+      <c r="B131" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C131" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D131" s="22"/>
+      <c r="E131" s="22"/>
+      <c r="F131" s="22"/>
+      <c r="G131" s="22"/>
+      <c r="H131" s="22"/>
+      <c r="I131" s="22"/>
+      <c r="J131" s="26"/>
+      <c r="K131" s="22"/>
+      <c r="L131" s="22"/>
+      <c r="M131" s="22"/>
+      <c r="N131" s="22"/>
+      <c r="O131" s="22"/>
+      <c r="P131" s="22"/>
+      <c r="Q131" s="22"/>
+      <c r="R131" s="22"/>
+      <c r="S131" s="22"/>
+      <c r="T131" s="22"/>
+      <c r="U131" s="22"/>
+      <c r="V131" s="22"/>
+      <c r="W131" s="22"/>
+      <c r="X131" s="22"/>
+      <c r="Y131" s="22"/>
+      <c r="Z131" s="22"/>
+    </row>
+    <row r="132" ht="12.0" customHeight="1">
+      <c r="A132" s="23"/>
+      <c r="B132" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C132" s="28">
         <v>-1.0E20</v>
       </c>
-      <c r="D118" s="27"/>
-      <c r="E118" s="27"/>
-      <c r="F118" s="27"/>
-      <c r="G118" s="27"/>
-      <c r="H118" s="27"/>
-      <c r="I118" s="27"/>
-      <c r="J118" s="28"/>
-      <c r="K118" s="27"/>
-      <c r="L118" s="27"/>
-      <c r="M118" s="27"/>
-      <c r="N118" s="27"/>
-      <c r="O118" s="27"/>
-      <c r="P118" s="27"/>
-      <c r="Q118" s="27"/>
-      <c r="R118" s="27"/>
-      <c r="S118" s="27"/>
-      <c r="T118" s="27"/>
-      <c r="U118" s="27"/>
-      <c r="V118" s="27"/>
-      <c r="W118" s="27"/>
-      <c r="X118" s="27"/>
-      <c r="Y118" s="27"/>
-      <c r="Z118" s="27"/>
-    </row>
-    <row r="119" ht="12.0" customHeight="1">
-      <c r="A119" s="24"/>
-      <c r="B119" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C119" s="32" t="s">
+      <c r="D132" s="22"/>
+      <c r="E132" s="22"/>
+      <c r="F132" s="22"/>
+      <c r="G132" s="22"/>
+      <c r="H132" s="22"/>
+      <c r="I132" s="22"/>
+      <c r="J132" s="26"/>
+      <c r="K132" s="22"/>
+      <c r="L132" s="22"/>
+      <c r="M132" s="22"/>
+      <c r="N132" s="22"/>
+      <c r="O132" s="22"/>
+      <c r="P132" s="22"/>
+      <c r="Q132" s="22"/>
+      <c r="R132" s="22"/>
+      <c r="S132" s="22"/>
+      <c r="T132" s="22"/>
+      <c r="U132" s="22"/>
+      <c r="V132" s="22"/>
+      <c r="W132" s="22"/>
+      <c r="X132" s="22"/>
+      <c r="Y132" s="22"/>
+      <c r="Z132" s="22"/>
+    </row>
+    <row r="133" ht="12.0" customHeight="1">
+      <c r="A133" s="23"/>
+      <c r="B133" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D119" s="27"/>
-      <c r="E119" s="27"/>
-      <c r="F119" s="27"/>
-      <c r="G119" s="27"/>
-      <c r="H119" s="27"/>
-      <c r="I119" s="27"/>
-      <c r="J119" s="28"/>
-      <c r="K119" s="27"/>
-      <c r="L119" s="27"/>
-      <c r="M119" s="27"/>
-      <c r="N119" s="27"/>
-      <c r="O119" s="27"/>
-      <c r="P119" s="27"/>
-      <c r="Q119" s="27"/>
-      <c r="R119" s="27"/>
-      <c r="S119" s="27"/>
-      <c r="T119" s="27"/>
-      <c r="U119" s="27"/>
-      <c r="V119" s="27"/>
-      <c r="W119" s="27"/>
-      <c r="X119" s="27"/>
-      <c r="Y119" s="27"/>
-      <c r="Z119" s="27"/>
-    </row>
-    <row r="120" ht="12.0" customHeight="1">
-      <c r="A120" s="24"/>
-      <c r="B120" s="27" t="s">
+      <c r="C133" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="C120" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="D120" s="27"/>
-      <c r="E120" s="27"/>
-      <c r="F120" s="27"/>
-      <c r="G120" s="27"/>
-      <c r="H120" s="27"/>
-      <c r="I120" s="27"/>
-      <c r="J120" s="28"/>
-      <c r="K120" s="27"/>
-      <c r="L120" s="27"/>
-      <c r="M120" s="27"/>
-      <c r="N120" s="27"/>
-      <c r="O120" s="27"/>
-      <c r="P120" s="27"/>
-      <c r="Q120" s="27"/>
-      <c r="R120" s="27"/>
-      <c r="S120" s="27"/>
-      <c r="T120" s="27"/>
-      <c r="U120" s="27"/>
-      <c r="V120" s="27"/>
-      <c r="W120" s="27"/>
-      <c r="X120" s="27"/>
-      <c r="Y120" s="27"/>
-      <c r="Z120" s="27"/>
-    </row>
-    <row r="121" ht="12.0" customHeight="1">
-      <c r="A121" s="24"/>
-      <c r="B121" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C121" s="28"/>
-      <c r="D121" s="27"/>
-      <c r="E121" s="27"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="27"/>
-      <c r="H121" s="27"/>
-      <c r="I121" s="27"/>
-      <c r="J121" s="28"/>
-      <c r="K121" s="27"/>
-      <c r="L121" s="27"/>
-      <c r="M121" s="27"/>
-      <c r="N121" s="27"/>
-      <c r="O121" s="27"/>
-      <c r="P121" s="27"/>
-      <c r="Q121" s="27"/>
-      <c r="R121" s="27"/>
-      <c r="S121" s="27"/>
-      <c r="T121" s="27"/>
-      <c r="U121" s="27"/>
-      <c r="V121" s="27"/>
-      <c r="W121" s="27"/>
-      <c r="X121" s="27"/>
-      <c r="Y121" s="27"/>
-      <c r="Z121" s="27"/>
-    </row>
-    <row r="122" ht="12.0" customHeight="1">
-      <c r="A122" s="24"/>
-      <c r="B122" s="27" t="s">
+      <c r="D133" s="22"/>
+      <c r="E133" s="22"/>
+      <c r="F133" s="22"/>
+      <c r="G133" s="22"/>
+      <c r="H133" s="22"/>
+      <c r="I133" s="22"/>
+      <c r="J133" s="26"/>
+      <c r="K133" s="22"/>
+      <c r="L133" s="22"/>
+      <c r="M133" s="22"/>
+      <c r="N133" s="22"/>
+      <c r="O133" s="22"/>
+      <c r="P133" s="22"/>
+      <c r="Q133" s="22"/>
+      <c r="R133" s="22"/>
+      <c r="S133" s="22"/>
+      <c r="T133" s="22"/>
+      <c r="U133" s="22"/>
+      <c r="V133" s="22"/>
+      <c r="W133" s="22"/>
+      <c r="X133" s="22"/>
+      <c r="Y133" s="22"/>
+      <c r="Z133" s="22"/>
+    </row>
+    <row r="134" ht="12.0" customHeight="1">
+      <c r="A134" s="23"/>
+      <c r="B134" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C122" s="29" t="s">
+      <c r="C134" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D134" s="22"/>
+      <c r="E134" s="22"/>
+      <c r="F134" s="22"/>
+      <c r="G134" s="22"/>
+      <c r="H134" s="22"/>
+      <c r="I134" s="22"/>
+      <c r="J134" s="26"/>
+      <c r="K134" s="22"/>
+      <c r="L134" s="22"/>
+      <c r="M134" s="22"/>
+      <c r="N134" s="22"/>
+      <c r="O134" s="22"/>
+      <c r="P134" s="22"/>
+      <c r="Q134" s="22"/>
+      <c r="R134" s="22"/>
+      <c r="S134" s="22"/>
+      <c r="T134" s="22"/>
+      <c r="U134" s="22"/>
+      <c r="V134" s="22"/>
+      <c r="W134" s="22"/>
+      <c r="X134" s="22"/>
+      <c r="Y134" s="22"/>
+      <c r="Z134" s="22"/>
+    </row>
+    <row r="135" ht="12.0" customHeight="1">
+      <c r="A135" s="23"/>
+      <c r="B135" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C135" s="26"/>
+      <c r="D135" s="22"/>
+      <c r="E135" s="22"/>
+      <c r="F135" s="22"/>
+      <c r="G135" s="22"/>
+      <c r="H135" s="22"/>
+      <c r="I135" s="22"/>
+      <c r="J135" s="26"/>
+      <c r="K135" s="22"/>
+      <c r="L135" s="22"/>
+      <c r="M135" s="22"/>
+      <c r="N135" s="22"/>
+      <c r="O135" s="22"/>
+      <c r="P135" s="22"/>
+      <c r="Q135" s="22"/>
+      <c r="R135" s="22"/>
+      <c r="S135" s="22"/>
+      <c r="T135" s="22"/>
+      <c r="U135" s="22"/>
+      <c r="V135" s="22"/>
+      <c r="W135" s="22"/>
+      <c r="X135" s="22"/>
+      <c r="Y135" s="22"/>
+      <c r="Z135" s="22"/>
+    </row>
+    <row r="136" ht="12.0" customHeight="1">
+      <c r="A136" s="23"/>
+      <c r="B136" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="D122" s="27"/>
-      <c r="E122" s="27"/>
-      <c r="F122" s="27"/>
-      <c r="G122" s="27"/>
-      <c r="H122" s="27"/>
-      <c r="I122" s="27"/>
-      <c r="J122" s="28"/>
-      <c r="K122" s="27"/>
-      <c r="L122" s="27"/>
-      <c r="M122" s="27"/>
-      <c r="N122" s="27"/>
-      <c r="O122" s="27"/>
-      <c r="P122" s="27"/>
-      <c r="Q122" s="27"/>
-      <c r="R122" s="27"/>
-      <c r="S122" s="27"/>
-      <c r="T122" s="27"/>
-      <c r="U122" s="27"/>
-      <c r="V122" s="27"/>
-      <c r="W122" s="27"/>
-      <c r="X122" s="27"/>
-      <c r="Y122" s="27"/>
-      <c r="Z122" s="27"/>
-    </row>
-    <row r="123" ht="12.0" customHeight="1">
-      <c r="A123" s="24"/>
-      <c r="B123" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C123" s="29"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="27"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="27"/>
-      <c r="H123" s="27"/>
-      <c r="I123" s="27"/>
-      <c r="J123" s="28"/>
-      <c r="K123" s="27"/>
-      <c r="L123" s="27"/>
-      <c r="M123" s="27"/>
-      <c r="N123" s="27"/>
-      <c r="O123" s="27"/>
-      <c r="P123" s="27"/>
-      <c r="Q123" s="27"/>
-      <c r="R123" s="27"/>
-      <c r="S123" s="27"/>
-      <c r="T123" s="27"/>
-      <c r="U123" s="27"/>
-      <c r="V123" s="27"/>
-      <c r="W123" s="27"/>
-      <c r="X123" s="27"/>
-      <c r="Y123" s="27"/>
-      <c r="Z123" s="27"/>
-    </row>
-    <row r="124" ht="12.0" customHeight="1">
-      <c r="A124" s="24"/>
-      <c r="B124" s="27" t="s">
+      <c r="C136" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D136" s="22"/>
+      <c r="E136" s="22"/>
+      <c r="F136" s="22"/>
+      <c r="G136" s="22"/>
+      <c r="H136" s="22"/>
+      <c r="I136" s="22"/>
+      <c r="J136" s="26"/>
+      <c r="K136" s="22"/>
+      <c r="L136" s="22"/>
+      <c r="M136" s="22"/>
+      <c r="N136" s="22"/>
+      <c r="O136" s="22"/>
+      <c r="P136" s="22"/>
+      <c r="Q136" s="22"/>
+      <c r="R136" s="22"/>
+      <c r="S136" s="22"/>
+      <c r="T136" s="22"/>
+      <c r="U136" s="22"/>
+      <c r="V136" s="22"/>
+      <c r="W136" s="22"/>
+      <c r="X136" s="22"/>
+      <c r="Y136" s="22"/>
+      <c r="Z136" s="22"/>
+    </row>
+    <row r="137" ht="12.0" customHeight="1">
+      <c r="A137" s="23"/>
+      <c r="B137" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="C124" s="29" t="s">
+      <c r="C137" s="27"/>
+      <c r="D137" s="22"/>
+      <c r="E137" s="22"/>
+      <c r="F137" s="22"/>
+      <c r="G137" s="22"/>
+      <c r="H137" s="22"/>
+      <c r="I137" s="22"/>
+      <c r="J137" s="26"/>
+      <c r="K137" s="22"/>
+      <c r="L137" s="22"/>
+      <c r="M137" s="22"/>
+      <c r="N137" s="22"/>
+      <c r="O137" s="22"/>
+      <c r="P137" s="22"/>
+      <c r="Q137" s="22"/>
+      <c r="R137" s="22"/>
+      <c r="S137" s="22"/>
+      <c r="T137" s="22"/>
+      <c r="U137" s="22"/>
+      <c r="V137" s="22"/>
+      <c r="W137" s="22"/>
+      <c r="X137" s="22"/>
+      <c r="Y137" s="22"/>
+      <c r="Z137" s="22"/>
+    </row>
+    <row r="138" ht="12.0" customHeight="1">
+      <c r="A138" s="23"/>
+      <c r="B138" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="D124" s="27"/>
-      <c r="E124" s="27"/>
-      <c r="F124" s="27"/>
-      <c r="G124" s="27"/>
-      <c r="H124" s="27"/>
-      <c r="I124" s="27"/>
-      <c r="J124" s="28"/>
-      <c r="K124" s="27"/>
-      <c r="L124" s="27"/>
-      <c r="M124" s="27"/>
-      <c r="N124" s="27"/>
-      <c r="O124" s="27"/>
-      <c r="P124" s="27"/>
-      <c r="Q124" s="27"/>
-      <c r="R124" s="27"/>
-      <c r="S124" s="27"/>
-      <c r="T124" s="27"/>
-      <c r="U124" s="27"/>
-      <c r="V124" s="27"/>
-      <c r="W124" s="27"/>
-      <c r="X124" s="27"/>
-      <c r="Y124" s="27"/>
-      <c r="Z124" s="27"/>
-    </row>
-    <row r="125" ht="12.0" customHeight="1">
-      <c r="A125" s="24"/>
-      <c r="B125" s="27"/>
-      <c r="C125" s="29"/>
-      <c r="D125" s="27"/>
-      <c r="E125" s="27"/>
-      <c r="F125" s="27"/>
-      <c r="G125" s="27"/>
-      <c r="H125" s="27"/>
-      <c r="I125" s="27"/>
-      <c r="J125" s="28"/>
-      <c r="K125" s="27"/>
-      <c r="L125" s="27"/>
-      <c r="M125" s="27"/>
-      <c r="N125" s="27"/>
-      <c r="O125" s="27"/>
-      <c r="P125" s="27"/>
-      <c r="Q125" s="27"/>
-      <c r="R125" s="27"/>
-      <c r="S125" s="27"/>
-      <c r="T125" s="27"/>
-      <c r="U125" s="27"/>
-      <c r="V125" s="27"/>
-      <c r="W125" s="27"/>
-      <c r="X125" s="27"/>
-      <c r="Y125" s="27"/>
-      <c r="Z125" s="27"/>
-    </row>
-    <row r="126" ht="12.0" customHeight="1">
-      <c r="A126" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="B126" s="24"/>
-      <c r="C126" s="25"/>
-      <c r="D126" s="27"/>
-      <c r="E126" s="27"/>
-      <c r="F126" s="27"/>
-      <c r="G126" s="27"/>
-      <c r="H126" s="27"/>
-      <c r="I126" s="27"/>
-      <c r="J126" s="28"/>
-      <c r="K126" s="27"/>
-      <c r="L126" s="27"/>
-      <c r="M126" s="27"/>
-      <c r="N126" s="27"/>
-      <c r="O126" s="27"/>
-      <c r="P126" s="27"/>
-      <c r="Q126" s="27"/>
-      <c r="R126" s="27"/>
-      <c r="S126" s="27"/>
-      <c r="T126" s="27"/>
-      <c r="U126" s="27"/>
-      <c r="V126" s="27"/>
-      <c r="W126" s="27"/>
-      <c r="X126" s="27"/>
-      <c r="Y126" s="27"/>
-      <c r="Z126" s="27"/>
-    </row>
-    <row r="127" ht="12.0" customHeight="1">
-      <c r="A127" s="24"/>
-      <c r="B127" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C127" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D127" s="27"/>
-      <c r="E127" s="27"/>
-      <c r="F127" s="27"/>
-      <c r="G127" s="27"/>
-      <c r="H127" s="27"/>
-      <c r="I127" s="27"/>
-      <c r="J127" s="28"/>
-      <c r="K127" s="27"/>
-      <c r="L127" s="27"/>
-      <c r="M127" s="27"/>
-      <c r="N127" s="27"/>
-      <c r="O127" s="27"/>
-      <c r="P127" s="27"/>
-      <c r="Q127" s="27"/>
-      <c r="R127" s="27"/>
-      <c r="S127" s="27"/>
-      <c r="T127" s="27"/>
-      <c r="U127" s="27"/>
-      <c r="V127" s="27"/>
-      <c r="W127" s="27"/>
-      <c r="X127" s="27"/>
-      <c r="Y127" s="27"/>
-      <c r="Z127" s="27"/>
-    </row>
-    <row r="128" ht="12.0" customHeight="1">
-      <c r="A128" s="24"/>
-      <c r="B128" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C128" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D128" s="27"/>
-      <c r="E128" s="27"/>
-      <c r="F128" s="27"/>
-      <c r="G128" s="27"/>
-      <c r="H128" s="27"/>
-      <c r="I128" s="27"/>
-      <c r="J128" s="28"/>
-      <c r="K128" s="27"/>
-      <c r="L128" s="27"/>
-      <c r="M128" s="27"/>
-      <c r="N128" s="27"/>
-      <c r="O128" s="27"/>
-      <c r="P128" s="27"/>
-      <c r="Q128" s="27"/>
-      <c r="R128" s="27"/>
-      <c r="S128" s="27"/>
-      <c r="T128" s="27"/>
-      <c r="U128" s="27"/>
-      <c r="V128" s="27"/>
-      <c r="W128" s="27"/>
-      <c r="X128" s="27"/>
-      <c r="Y128" s="27"/>
-      <c r="Z128" s="27"/>
-    </row>
-    <row r="129" ht="12.0" customHeight="1">
-      <c r="A129" s="24"/>
-      <c r="B129" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C129" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D129" s="27"/>
-      <c r="E129" s="27"/>
-      <c r="F129" s="27"/>
-      <c r="G129" s="27"/>
-      <c r="H129" s="27"/>
-      <c r="I129" s="27"/>
-      <c r="J129" s="28"/>
-      <c r="K129" s="27"/>
-      <c r="L129" s="27"/>
-      <c r="M129" s="27"/>
-      <c r="N129" s="27"/>
-      <c r="O129" s="27"/>
-      <c r="P129" s="27"/>
-      <c r="Q129" s="27"/>
-      <c r="R129" s="27"/>
-      <c r="S129" s="27"/>
-      <c r="T129" s="27"/>
-      <c r="U129" s="27"/>
-      <c r="V129" s="27"/>
-      <c r="W129" s="27"/>
-      <c r="X129" s="27"/>
-      <c r="Y129" s="27"/>
-      <c r="Z129" s="27"/>
-    </row>
-    <row r="130" ht="12.0" customHeight="1">
-      <c r="A130" s="24"/>
-      <c r="B130" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C130" s="25"/>
-      <c r="D130" s="27"/>
-      <c r="E130" s="27"/>
-      <c r="F130" s="27"/>
-      <c r="G130" s="27"/>
-      <c r="H130" s="27"/>
-      <c r="I130" s="27"/>
-      <c r="J130" s="28"/>
-      <c r="K130" s="27"/>
-      <c r="L130" s="27"/>
-      <c r="M130" s="27"/>
-      <c r="N130" s="27"/>
-      <c r="O130" s="27"/>
-      <c r="P130" s="27"/>
-      <c r="Q130" s="27"/>
-      <c r="R130" s="27"/>
-      <c r="S130" s="27"/>
-      <c r="T130" s="27"/>
-      <c r="U130" s="27"/>
-      <c r="V130" s="27"/>
-      <c r="W130" s="27"/>
-      <c r="X130" s="27"/>
-      <c r="Y130" s="27"/>
-      <c r="Z130" s="27"/>
-    </row>
-    <row r="131" ht="12.0" customHeight="1">
-      <c r="A131" s="24"/>
-      <c r="B131" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C131" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="D131" s="27"/>
-      <c r="E131" s="27"/>
-      <c r="F131" s="27"/>
-      <c r="G131" s="27"/>
-      <c r="H131" s="27"/>
-      <c r="I131" s="27"/>
-      <c r="J131" s="28"/>
-      <c r="K131" s="27"/>
-      <c r="L131" s="27"/>
-      <c r="M131" s="27"/>
-      <c r="N131" s="27"/>
-      <c r="O131" s="27"/>
-      <c r="P131" s="27"/>
-      <c r="Q131" s="27"/>
-      <c r="R131" s="27"/>
-      <c r="S131" s="27"/>
-      <c r="T131" s="27"/>
-      <c r="U131" s="27"/>
-      <c r="V131" s="27"/>
-      <c r="W131" s="27"/>
-      <c r="X131" s="27"/>
-      <c r="Y131" s="27"/>
-      <c r="Z131" s="27"/>
-    </row>
-    <row r="132" ht="12.0" customHeight="1">
-      <c r="A132" s="24"/>
-      <c r="B132" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C132" s="31">
-        <v>-1.0E20</v>
-      </c>
-      <c r="D132" s="27"/>
-      <c r="E132" s="27"/>
-      <c r="F132" s="27"/>
-      <c r="G132" s="27"/>
-      <c r="H132" s="27"/>
-      <c r="I132" s="27"/>
-      <c r="J132" s="28"/>
-      <c r="K132" s="27"/>
-      <c r="L132" s="27"/>
-      <c r="M132" s="27"/>
-      <c r="N132" s="27"/>
-      <c r="O132" s="27"/>
-      <c r="P132" s="27"/>
-      <c r="Q132" s="27"/>
-      <c r="R132" s="27"/>
-      <c r="S132" s="27"/>
-      <c r="T132" s="27"/>
-      <c r="U132" s="27"/>
-      <c r="V132" s="27"/>
-      <c r="W132" s="27"/>
-      <c r="X132" s="27"/>
-      <c r="Y132" s="27"/>
-      <c r="Z132" s="27"/>
-    </row>
-    <row r="133" ht="12.0" customHeight="1">
-      <c r="A133" s="24"/>
-      <c r="B133" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C133" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="D133" s="27"/>
-      <c r="E133" s="27"/>
-      <c r="F133" s="27"/>
-      <c r="G133" s="27"/>
-      <c r="H133" s="27"/>
-      <c r="I133" s="27"/>
-      <c r="J133" s="28"/>
-      <c r="K133" s="27"/>
-      <c r="L133" s="27"/>
-      <c r="M133" s="27"/>
-      <c r="N133" s="27"/>
-      <c r="O133" s="27"/>
-      <c r="P133" s="27"/>
-      <c r="Q133" s="27"/>
-      <c r="R133" s="27"/>
-      <c r="S133" s="27"/>
-      <c r="T133" s="27"/>
-      <c r="U133" s="27"/>
-      <c r="V133" s="27"/>
-      <c r="W133" s="27"/>
-      <c r="X133" s="27"/>
-      <c r="Y133" s="27"/>
-      <c r="Z133" s="27"/>
-    </row>
-    <row r="134" ht="12.0" customHeight="1">
-      <c r="A134" s="24"/>
-      <c r="B134" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C134" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="D134" s="27"/>
-      <c r="E134" s="27"/>
-      <c r="F134" s="27"/>
-      <c r="G134" s="27"/>
-      <c r="H134" s="27"/>
-      <c r="I134" s="27"/>
-      <c r="J134" s="28"/>
-      <c r="K134" s="27"/>
-      <c r="L134" s="27"/>
-      <c r="M134" s="27"/>
-      <c r="N134" s="27"/>
-      <c r="O134" s="27"/>
-      <c r="P134" s="27"/>
-      <c r="Q134" s="27"/>
-      <c r="R134" s="27"/>
-      <c r="S134" s="27"/>
-      <c r="T134" s="27"/>
-      <c r="U134" s="27"/>
-      <c r="V134" s="27"/>
-      <c r="W134" s="27"/>
-      <c r="X134" s="27"/>
-      <c r="Y134" s="27"/>
-      <c r="Z134" s="27"/>
-    </row>
-    <row r="135" ht="12.0" customHeight="1">
-      <c r="A135" s="24"/>
-      <c r="B135" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C135" s="28"/>
-      <c r="D135" s="27"/>
-      <c r="E135" s="27"/>
-      <c r="F135" s="27"/>
-      <c r="G135" s="27"/>
-      <c r="H135" s="27"/>
-      <c r="I135" s="27"/>
-      <c r="J135" s="28"/>
-      <c r="K135" s="27"/>
-      <c r="L135" s="27"/>
-      <c r="M135" s="27"/>
-      <c r="N135" s="27"/>
-      <c r="O135" s="27"/>
-      <c r="P135" s="27"/>
-      <c r="Q135" s="27"/>
-      <c r="R135" s="27"/>
-      <c r="S135" s="27"/>
-      <c r="T135" s="27"/>
-      <c r="U135" s="27"/>
-      <c r="V135" s="27"/>
-      <c r="W135" s="27"/>
-      <c r="X135" s="27"/>
-      <c r="Y135" s="27"/>
-      <c r="Z135" s="27"/>
-    </row>
-    <row r="136" ht="12.0" customHeight="1">
-      <c r="A136" s="24"/>
-      <c r="B136" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C136" s="29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D136" s="27"/>
-      <c r="E136" s="27"/>
-      <c r="F136" s="27"/>
-      <c r="G136" s="27"/>
-      <c r="H136" s="27"/>
-      <c r="I136" s="27"/>
-      <c r="J136" s="28"/>
-      <c r="K136" s="27"/>
-      <c r="L136" s="27"/>
-      <c r="M136" s="27"/>
-      <c r="N136" s="27"/>
-      <c r="O136" s="27"/>
-      <c r="P136" s="27"/>
-      <c r="Q136" s="27"/>
-      <c r="R136" s="27"/>
-      <c r="S136" s="27"/>
-      <c r="T136" s="27"/>
-      <c r="U136" s="27"/>
-      <c r="V136" s="27"/>
-      <c r="W136" s="27"/>
-      <c r="X136" s="27"/>
-      <c r="Y136" s="27"/>
-      <c r="Z136" s="27"/>
-    </row>
-    <row r="137" ht="12.0" customHeight="1">
-      <c r="A137" s="24"/>
-      <c r="B137" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="C137" s="29"/>
-      <c r="D137" s="27"/>
-      <c r="E137" s="27"/>
-      <c r="F137" s="27"/>
-      <c r="G137" s="27"/>
-      <c r="H137" s="27"/>
-      <c r="I137" s="27"/>
-      <c r="J137" s="28"/>
-      <c r="K137" s="27"/>
-      <c r="L137" s="27"/>
-      <c r="M137" s="27"/>
-      <c r="N137" s="27"/>
-      <c r="O137" s="27"/>
-      <c r="P137" s="27"/>
-      <c r="Q137" s="27"/>
-      <c r="R137" s="27"/>
-      <c r="S137" s="27"/>
-      <c r="T137" s="27"/>
-      <c r="U137" s="27"/>
-      <c r="V137" s="27"/>
-      <c r="W137" s="27"/>
-      <c r="X137" s="27"/>
-      <c r="Y137" s="27"/>
-      <c r="Z137" s="27"/>
-    </row>
-    <row r="138" ht="12.0" customHeight="1">
-      <c r="A138" s="24"/>
-      <c r="B138" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C138" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="D138" s="27"/>
-      <c r="E138" s="27"/>
-      <c r="F138" s="27"/>
-      <c r="G138" s="27"/>
-      <c r="H138" s="27"/>
-      <c r="I138" s="27"/>
-      <c r="J138" s="28"/>
-      <c r="K138" s="27"/>
-      <c r="L138" s="27"/>
-      <c r="M138" s="27"/>
-      <c r="N138" s="27"/>
-      <c r="O138" s="27"/>
-      <c r="P138" s="27"/>
-      <c r="Q138" s="27"/>
-      <c r="R138" s="27"/>
-      <c r="S138" s="27"/>
-      <c r="T138" s="27"/>
-      <c r="U138" s="27"/>
-      <c r="V138" s="27"/>
-      <c r="W138" s="27"/>
-      <c r="X138" s="27"/>
-      <c r="Y138" s="27"/>
-      <c r="Z138" s="27"/>
+      <c r="C138" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D138" s="22"/>
+      <c r="E138" s="22"/>
+      <c r="F138" s="22"/>
+      <c r="G138" s="22"/>
+      <c r="H138" s="22"/>
+      <c r="I138" s="22"/>
+      <c r="J138" s="26"/>
+      <c r="K138" s="22"/>
+      <c r="L138" s="22"/>
+      <c r="M138" s="22"/>
+      <c r="N138" s="22"/>
+      <c r="O138" s="22"/>
+      <c r="P138" s="22"/>
+      <c r="Q138" s="22"/>
+      <c r="R138" s="22"/>
+      <c r="S138" s="22"/>
+      <c r="T138" s="22"/>
+      <c r="U138" s="22"/>
+      <c r="V138" s="22"/>
+      <c r="W138" s="22"/>
+      <c r="X138" s="22"/>
+      <c r="Y138" s="22"/>
+      <c r="Z138" s="22"/>
     </row>
     <row r="139" ht="12.0" customHeight="1">
-      <c r="A139" s="24"/>
-      <c r="B139" s="27"/>
-      <c r="C139" s="29"/>
-      <c r="D139" s="27"/>
-      <c r="E139" s="27"/>
-      <c r="F139" s="27"/>
-      <c r="G139" s="27"/>
-      <c r="H139" s="27"/>
-      <c r="I139" s="27"/>
-      <c r="J139" s="28"/>
-      <c r="K139" s="27"/>
-      <c r="L139" s="27"/>
-      <c r="M139" s="27"/>
-      <c r="N139" s="27"/>
-      <c r="O139" s="27"/>
-      <c r="P139" s="27"/>
-      <c r="Q139" s="27"/>
-      <c r="R139" s="27"/>
-      <c r="S139" s="27"/>
-      <c r="T139" s="27"/>
-      <c r="U139" s="27"/>
-      <c r="V139" s="27"/>
-      <c r="W139" s="27"/>
-      <c r="X139" s="27"/>
-      <c r="Y139" s="27"/>
-      <c r="Z139" s="27"/>
+      <c r="A139" s="23"/>
+      <c r="B139" s="22"/>
+      <c r="C139" s="27"/>
+      <c r="D139" s="22"/>
+      <c r="E139" s="22"/>
+      <c r="F139" s="22"/>
+      <c r="G139" s="22"/>
+      <c r="H139" s="22"/>
+      <c r="I139" s="22"/>
+      <c r="J139" s="26"/>
+      <c r="K139" s="22"/>
+      <c r="L139" s="22"/>
+      <c r="M139" s="22"/>
+      <c r="N139" s="22"/>
+      <c r="O139" s="22"/>
+      <c r="P139" s="22"/>
+      <c r="Q139" s="22"/>
+      <c r="R139" s="22"/>
+      <c r="S139" s="22"/>
+      <c r="T139" s="22"/>
+      <c r="U139" s="22"/>
+      <c r="V139" s="22"/>
+      <c r="W139" s="22"/>
+      <c r="X139" s="22"/>
+      <c r="Y139" s="22"/>
+      <c r="Z139" s="22"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B140" s="10"/>
-      <c r="C140" s="18"/>
+      <c r="C140" s="17"/>
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
@@ -13567,10 +13562,10 @@
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="10"/>
       <c r="B141" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C141" s="18" t="s">
         <v>24</v>
+      </c>
+      <c r="C141" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
@@ -13598,10 +13593,10 @@
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="10"/>
       <c r="B142" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D142" s="6"/>
       <c r="E142" s="6"/>
@@ -13629,9 +13624,9 @@
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="10"/>
       <c r="B143" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C143" s="18">
+        <v>15</v>
+      </c>
+      <c r="C143" s="17">
         <v>1.0</v>
       </c>
       <c r="D143" s="6"/>
@@ -13660,11 +13655,11 @@
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="10"/>
       <c r="B144" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C144" s="8"/>
+        <v>28</v>
+      </c>
+      <c r="C144" s="7"/>
       <c r="D144" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E144" s="6"/>
       <c r="F144" s="6"/>
@@ -13691,10 +13686,10 @@
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="10"/>
       <c r="B145" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C145" s="34" t="s">
-        <v>66</v>
+        <v>29</v>
+      </c>
+      <c r="C145" s="31" t="s">
+        <v>67</v>
       </c>
       <c r="D145" s="6"/>
       <c r="E145" s="6"/>
@@ -13722,9 +13717,9 @@
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="10"/>
       <c r="B146" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C146" s="21">
+        <v>44</v>
+      </c>
+      <c r="C146" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D146" s="6"/>
@@ -13753,10 +13748,10 @@
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="10"/>
       <c r="B147" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C147" s="19" t="s">
         <v>31</v>
+      </c>
+      <c r="C147" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="D147" s="6"/>
       <c r="E147" s="6"/>
@@ -13784,13 +13779,13 @@
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="14"/>
       <c r="B148" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C148" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C148" s="19" t="s">
-        <v>31</v>
-      </c>
       <c r="D148" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E148" s="6"/>
       <c r="F148" s="6"/>
@@ -13816,10 +13811,10 @@
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="14"/>
-      <c r="B149" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C149" s="18"/>
+      <c r="B149" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C149" s="17"/>
       <c r="D149" s="6"/>
       <c r="E149" s="6"/>
       <c r="F149" s="6"/>
@@ -13846,10 +13841,10 @@
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="6"/>
       <c r="B150" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D150" s="6"/>
       <c r="E150" s="6"/>
@@ -13903,7 +13898,7 @@
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B152" s="10"/>
       <c r="C152" s="11"/>
@@ -13933,10 +13928,10 @@
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="10"/>
       <c r="B153" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
@@ -13964,10 +13959,10 @@
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="10"/>
       <c r="B154" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D154" s="6"/>
       <c r="E154" s="6"/>
@@ -13995,10 +13990,10 @@
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="10"/>
       <c r="B155" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
@@ -14026,11 +14021,11 @@
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="10"/>
       <c r="B156" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C156" s="11"/>
       <c r="D156" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E156" s="6"/>
       <c r="F156" s="6"/>
@@ -14057,10 +14052,10 @@
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="10"/>
       <c r="B157" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D157" s="6"/>
       <c r="E157" s="6"/>
@@ -14088,9 +14083,9 @@
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="10"/>
       <c r="B158" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C158" s="21">
+        <v>44</v>
+      </c>
+      <c r="C158" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D158" s="6"/>
@@ -14119,10 +14114,10 @@
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="10"/>
       <c r="B159" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C159" s="19" t="s">
         <v>31</v>
+      </c>
+      <c r="C159" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="D159" s="6"/>
       <c r="E159" s="6"/>
@@ -14150,10 +14145,10 @@
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="10"/>
       <c r="B160" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C160" s="18" t="s">
         <v>32</v>
-      </c>
-      <c r="C160" s="19" t="s">
-        <v>31</v>
       </c>
       <c r="D160" s="6"/>
       <c r="E160" s="6"/>
@@ -14180,13 +14175,13 @@
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="10"/>
-      <c r="B161" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C161" s="18"/>
+      <c r="B161" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C161" s="17"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F161" s="6"/>
       <c r="G161" s="6"/>
@@ -14212,10 +14207,10 @@
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="10"/>
       <c r="B162" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D162" s="6"/>
       <c r="E162" s="6"/>
@@ -14243,7 +14238,7 @@
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="10"/>
       <c r="B163" s="10"/>
-      <c r="C163" s="18"/>
+      <c r="C163" s="17"/>
       <c r="D163" s="6"/>
       <c r="E163" s="6"/>
       <c r="F163" s="6"/>
@@ -14269,7 +14264,7 @@
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B164" s="10"/>
       <c r="C164" s="11"/>
@@ -14299,10 +14294,10 @@
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="10"/>
       <c r="B165" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D165" s="6"/>
       <c r="E165" s="6"/>
@@ -14330,10 +14325,10 @@
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="10"/>
       <c r="B166" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D166" s="6"/>
       <c r="E166" s="6"/>
@@ -14361,10 +14356,10 @@
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="10"/>
       <c r="B167" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D167" s="6"/>
       <c r="E167" s="6"/>
@@ -14392,11 +14387,11 @@
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="10"/>
       <c r="B168" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C168" s="11"/>
       <c r="D168" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E168" s="6"/>
       <c r="F168" s="6"/>
@@ -14423,10 +14418,10 @@
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="10"/>
       <c r="B169" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D169" s="6"/>
       <c r="E169" s="6"/>
@@ -14454,9 +14449,9 @@
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="10"/>
       <c r="B170" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C170" s="21">
+        <v>44</v>
+      </c>
+      <c r="C170" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D170" s="6"/>
@@ -14485,10 +14480,10 @@
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="10"/>
       <c r="B171" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C171" s="19" t="s">
         <v>31</v>
+      </c>
+      <c r="C171" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="D171" s="6"/>
       <c r="E171" s="6"/>
@@ -14516,10 +14511,10 @@
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="10"/>
       <c r="B172" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C172" s="18" t="s">
         <v>32</v>
-      </c>
-      <c r="C172" s="19" t="s">
-        <v>31</v>
       </c>
       <c r="D172" s="6"/>
       <c r="E172" s="6"/>
@@ -14546,13 +14541,13 @@
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="10"/>
-      <c r="B173" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C173" s="18"/>
+      <c r="B173" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C173" s="17"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F173" s="6"/>
       <c r="G173" s="6"/>
@@ -14578,10 +14573,10 @@
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="10"/>
       <c r="B174" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D174" s="6"/>
       <c r="E174" s="6"/>
@@ -14635,10 +14630,10 @@
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B176" s="10"/>
-      <c r="C176" s="18"/>
+      <c r="C176" s="17"/>
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
       <c r="F176" s="6"/>
@@ -14665,10 +14660,10 @@
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="10"/>
       <c r="B177" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C177" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
@@ -14696,10 +14691,10 @@
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="10"/>
       <c r="B178" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C178" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D178" s="6"/>
       <c r="E178" s="6"/>
@@ -14727,7 +14722,7 @@
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="10"/>
       <c r="B179" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C179" s="11">
         <v>1.0</v>
@@ -14758,7 +14753,7 @@
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="10"/>
       <c r="B180" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C180" s="11"/>
       <c r="D180" s="6"/>
@@ -14787,10 +14782,10 @@
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="10"/>
       <c r="B181" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
@@ -14818,10 +14813,10 @@
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="10"/>
       <c r="B182" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C182" s="18" t="s">
         <v>78</v>
+      </c>
+      <c r="C182" s="17" t="s">
+        <v>79</v>
       </c>
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
@@ -14849,10 +14844,10 @@
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="10"/>
       <c r="B183" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C183" s="35" t="s">
         <v>80</v>
+      </c>
+      <c r="C183" s="32" t="s">
+        <v>81</v>
       </c>
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
@@ -14906,10 +14901,10 @@
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B185" s="10"/>
-      <c r="C185" s="18"/>
+      <c r="C185" s="17"/>
       <c r="D185" s="6"/>
       <c r="E185" s="6"/>
       <c r="F185" s="6"/>
@@ -14936,10 +14931,10 @@
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="10"/>
       <c r="B186" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C186" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D186" s="6"/>
       <c r="E186" s="6"/>
@@ -14967,10 +14962,10 @@
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="10"/>
       <c r="B187" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C187" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D187" s="6"/>
       <c r="E187" s="6"/>
@@ -14998,7 +14993,7 @@
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="10"/>
       <c r="B188" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C188" s="11">
         <v>1.0</v>
@@ -15029,7 +15024,7 @@
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="10"/>
       <c r="B189" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C189" s="11"/>
       <c r="D189" s="6"/>
@@ -15058,10 +15053,10 @@
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="10"/>
       <c r="B190" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C190" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D190" s="6"/>
       <c r="E190" s="6"/>
@@ -15089,10 +15084,10 @@
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="10"/>
       <c r="B191" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C191" s="18" t="s">
         <v>78</v>
+      </c>
+      <c r="C191" s="17" t="s">
+        <v>79</v>
       </c>
       <c r="D191" s="6"/>
       <c r="E191" s="6"/>
@@ -15120,10 +15115,10 @@
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="10"/>
       <c r="B192" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C192" s="35" t="s">
         <v>80</v>
+      </c>
+      <c r="C192" s="32" t="s">
+        <v>81</v>
       </c>
       <c r="D192" s="6"/>
       <c r="E192" s="6"/>
@@ -15177,10 +15172,10 @@
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B194" s="10"/>
-      <c r="C194" s="18"/>
+      <c r="C194" s="17"/>
       <c r="D194" s="6"/>
       <c r="E194" s="6"/>
       <c r="F194" s="6"/>
@@ -15207,10 +15202,10 @@
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="10"/>
       <c r="B195" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D195" s="6"/>
       <c r="E195" s="6"/>
@@ -15238,10 +15233,10 @@
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="10"/>
       <c r="B196" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D196" s="6"/>
       <c r="E196" s="6"/>
@@ -15269,7 +15264,7 @@
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="10"/>
       <c r="B197" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C197" s="11">
         <v>1.0</v>
@@ -15300,7 +15295,7 @@
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="10"/>
       <c r="B198" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C198" s="11"/>
       <c r="D198" s="6"/>
@@ -15329,10 +15324,10 @@
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="10"/>
       <c r="B199" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C199" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D199" s="6"/>
       <c r="E199" s="6"/>
@@ -15360,10 +15355,10 @@
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="10"/>
       <c r="B200" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C200" s="18" t="s">
         <v>78</v>
+      </c>
+      <c r="C200" s="17" t="s">
+        <v>79</v>
       </c>
       <c r="D200" s="6"/>
       <c r="E200" s="6"/>
@@ -15391,10 +15386,10 @@
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="10"/>
       <c r="B201" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C201" s="35" t="s">
         <v>80</v>
+      </c>
+      <c r="C201" s="32" t="s">
+        <v>81</v>
       </c>
       <c r="D201" s="6"/>
       <c r="E201" s="6"/>
@@ -15448,10 +15443,10 @@
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B203" s="10"/>
-      <c r="C203" s="18"/>
+      <c r="C203" s="17"/>
       <c r="D203" s="6"/>
       <c r="E203" s="6"/>
       <c r="F203" s="6"/>
@@ -15478,10 +15473,10 @@
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="10"/>
       <c r="B204" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D204" s="6"/>
       <c r="E204" s="6"/>
@@ -15509,10 +15504,10 @@
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="10"/>
       <c r="B205" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C205" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D205" s="6"/>
       <c r="E205" s="6"/>
@@ -15540,7 +15535,7 @@
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="10"/>
       <c r="B206" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C206" s="11">
         <v>1.0</v>
@@ -15571,7 +15566,7 @@
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="10"/>
       <c r="B207" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C207" s="11"/>
       <c r="D207" s="6"/>
@@ -15600,10 +15595,10 @@
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="10"/>
       <c r="B208" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D208" s="6"/>
       <c r="E208" s="6"/>
@@ -15631,10 +15626,10 @@
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="10"/>
       <c r="B209" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C209" s="18" t="s">
         <v>78</v>
+      </c>
+      <c r="C209" s="17" t="s">
+        <v>79</v>
       </c>
       <c r="D209" s="6"/>
       <c r="E209" s="6"/>
@@ -15659,13 +15654,13 @@
       <c r="X209" s="6"/>
       <c r="Y209" s="6"/>
     </row>
-    <row r="210">
+    <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="10"/>
       <c r="B210" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C210" s="35" t="s">
         <v>80</v>
+      </c>
+      <c r="C210" s="32" t="s">
+        <v>81</v>
       </c>
       <c r="D210" s="6"/>
       <c r="E210" s="6"/>
@@ -20364,7 +20359,7 @@
     <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="6"/>
       <c r="B384" s="6"/>
-      <c r="C384" s="8"/>
+      <c r="C384" s="7"/>
       <c r="D384" s="6"/>
       <c r="E384" s="6"/>
       <c r="F384" s="6"/>
@@ -20391,7 +20386,7 @@
     <row r="385" ht="15.75" customHeight="1">
       <c r="A385" s="6"/>
       <c r="B385" s="6"/>
-      <c r="C385" s="8"/>
+      <c r="C385" s="7"/>
       <c r="D385" s="6"/>
       <c r="E385" s="6"/>
       <c r="F385" s="6"/>
@@ -20418,7 +20413,7 @@
     <row r="386" ht="15.75" customHeight="1">
       <c r="A386" s="6"/>
       <c r="B386" s="6"/>
-      <c r="C386" s="8"/>
+      <c r="C386" s="7"/>
       <c r="D386" s="6"/>
       <c r="E386" s="6"/>
       <c r="F386" s="6"/>
@@ -20445,7 +20440,7 @@
     <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="6"/>
       <c r="B387" s="6"/>
-      <c r="C387" s="8"/>
+      <c r="C387" s="7"/>
       <c r="D387" s="6"/>
       <c r="E387" s="6"/>
       <c r="F387" s="6"/>
@@ -20472,7 +20467,7 @@
     <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="6"/>
       <c r="B388" s="6"/>
-      <c r="C388" s="8"/>
+      <c r="C388" s="7"/>
       <c r="D388" s="6"/>
       <c r="E388" s="6"/>
       <c r="F388" s="6"/>
@@ -20499,7 +20494,7 @@
     <row r="389" ht="15.75" customHeight="1">
       <c r="A389" s="6"/>
       <c r="B389" s="6"/>
-      <c r="C389" s="8"/>
+      <c r="C389" s="7"/>
       <c r="D389" s="6"/>
       <c r="E389" s="6"/>
       <c r="F389" s="6"/>
@@ -20526,7 +20521,7 @@
     <row r="390" ht="15.75" customHeight="1">
       <c r="A390" s="6"/>
       <c r="B390" s="6"/>
-      <c r="C390" s="8"/>
+      <c r="C390" s="7"/>
       <c r="D390" s="6"/>
       <c r="E390" s="6"/>
       <c r="F390" s="6"/>
@@ -20553,7 +20548,7 @@
     <row r="391" ht="15.75" customHeight="1">
       <c r="A391" s="6"/>
       <c r="B391" s="6"/>
-      <c r="C391" s="8"/>
+      <c r="C391" s="7"/>
       <c r="D391" s="6"/>
       <c r="E391" s="6"/>
       <c r="F391" s="6"/>
@@ -20580,7 +20575,7 @@
     <row r="392" ht="15.75" customHeight="1">
       <c r="A392" s="6"/>
       <c r="B392" s="6"/>
-      <c r="C392" s="8"/>
+      <c r="C392" s="7"/>
       <c r="D392" s="6"/>
       <c r="E392" s="6"/>
       <c r="F392" s="6"/>
@@ -20607,7 +20602,7 @@
     <row r="393" ht="15.75" customHeight="1">
       <c r="A393" s="6"/>
       <c r="B393" s="6"/>
-      <c r="C393" s="8"/>
+      <c r="C393" s="7"/>
       <c r="D393" s="6"/>
       <c r="E393" s="6"/>
       <c r="F393" s="6"/>
@@ -20634,7 +20629,7 @@
     <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="6"/>
       <c r="B394" s="6"/>
-      <c r="C394" s="8"/>
+      <c r="C394" s="7"/>
       <c r="D394" s="6"/>
       <c r="E394" s="6"/>
       <c r="F394" s="6"/>
@@ -20661,7 +20656,7 @@
     <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="6"/>
       <c r="B395" s="6"/>
-      <c r="C395" s="8"/>
+      <c r="C395" s="7"/>
       <c r="D395" s="6"/>
       <c r="E395" s="6"/>
       <c r="F395" s="6"/>
@@ -20688,7 +20683,7 @@
     <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="6"/>
       <c r="B396" s="6"/>
-      <c r="C396" s="8"/>
+      <c r="C396" s="7"/>
       <c r="D396" s="6"/>
       <c r="E396" s="6"/>
       <c r="F396" s="6"/>
@@ -20715,7 +20710,7 @@
     <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="6"/>
       <c r="B397" s="6"/>
-      <c r="C397" s="8"/>
+      <c r="C397" s="7"/>
       <c r="D397" s="6"/>
       <c r="E397" s="6"/>
       <c r="F397" s="6"/>
@@ -20742,7 +20737,7 @@
     <row r="398" ht="15.75" customHeight="1">
       <c r="A398" s="6"/>
       <c r="B398" s="6"/>
-      <c r="C398" s="8"/>
+      <c r="C398" s="7"/>
       <c r="D398" s="6"/>
       <c r="E398" s="6"/>
       <c r="F398" s="6"/>
@@ -20769,7 +20764,7 @@
     <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="6"/>
       <c r="B399" s="6"/>
-      <c r="C399" s="8"/>
+      <c r="C399" s="7"/>
       <c r="D399" s="6"/>
       <c r="E399" s="6"/>
       <c r="F399" s="6"/>
@@ -20796,7 +20791,7 @@
     <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="6"/>
       <c r="B400" s="6"/>
-      <c r="C400" s="8"/>
+      <c r="C400" s="7"/>
       <c r="D400" s="6"/>
       <c r="E400" s="6"/>
       <c r="F400" s="6"/>
@@ -20823,7 +20818,7 @@
     <row r="401" ht="15.75" customHeight="1">
       <c r="A401" s="6"/>
       <c r="B401" s="6"/>
-      <c r="C401" s="8"/>
+      <c r="C401" s="7"/>
       <c r="D401" s="6"/>
       <c r="E401" s="6"/>
       <c r="F401" s="6"/>
@@ -20850,7 +20845,7 @@
     <row r="402" ht="15.75" customHeight="1">
       <c r="A402" s="6"/>
       <c r="B402" s="6"/>
-      <c r="C402" s="8"/>
+      <c r="C402" s="7"/>
       <c r="D402" s="6"/>
       <c r="E402" s="6"/>
       <c r="F402" s="6"/>
@@ -20877,7 +20872,7 @@
     <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="6"/>
       <c r="B403" s="6"/>
-      <c r="C403" s="8"/>
+      <c r="C403" s="7"/>
       <c r="D403" s="6"/>
       <c r="E403" s="6"/>
       <c r="F403" s="6"/>
@@ -20904,7 +20899,7 @@
     <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="6"/>
       <c r="B404" s="6"/>
-      <c r="C404" s="8"/>
+      <c r="C404" s="7"/>
       <c r="D404" s="6"/>
       <c r="E404" s="6"/>
       <c r="F404" s="6"/>
@@ -20931,7 +20926,7 @@
     <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="6"/>
       <c r="B405" s="6"/>
-      <c r="C405" s="8"/>
+      <c r="C405" s="7"/>
       <c r="D405" s="6"/>
       <c r="E405" s="6"/>
       <c r="F405" s="6"/>
@@ -20958,7 +20953,7 @@
     <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="6"/>
       <c r="B406" s="6"/>
-      <c r="C406" s="8"/>
+      <c r="C406" s="7"/>
       <c r="D406" s="6"/>
       <c r="E406" s="6"/>
       <c r="F406" s="6"/>
@@ -20985,7 +20980,7 @@
     <row r="407" ht="15.75" customHeight="1">
       <c r="A407" s="6"/>
       <c r="B407" s="6"/>
-      <c r="C407" s="8"/>
+      <c r="C407" s="7"/>
       <c r="D407" s="6"/>
       <c r="E407" s="6"/>
       <c r="F407" s="6"/>
@@ -21012,7 +21007,7 @@
     <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="6"/>
       <c r="B408" s="6"/>
-      <c r="C408" s="8"/>
+      <c r="C408" s="7"/>
       <c r="D408" s="6"/>
       <c r="E408" s="6"/>
       <c r="F408" s="6"/>
@@ -21039,7 +21034,7 @@
     <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="6"/>
       <c r="B409" s="6"/>
-      <c r="C409" s="8"/>
+      <c r="C409" s="7"/>
       <c r="D409" s="6"/>
       <c r="E409" s="6"/>
       <c r="F409" s="6"/>
@@ -21066,7 +21061,7 @@
     <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="6"/>
       <c r="B410" s="6"/>
-      <c r="C410" s="8"/>
+      <c r="C410" s="7"/>
       <c r="D410" s="6"/>
       <c r="E410" s="6"/>
       <c r="F410" s="6"/>
